--- a/website/assets/files/FY2016_Dataset.xlsx
+++ b/website/assets/files/FY2016_Dataset.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11003"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fowlkes_d\Work Folders\Documents\PaymentAccuracy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffhawley/source/omb-payment-accuracy/website/assets/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4DC02B-166F-E046-8358-7174A982AD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6840" tabRatio="782" firstSheet="4" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27880" windowHeight="17580" tabRatio="782" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agency Results" sheetId="16" r:id="rId1"/>
@@ -1736,7 +1737,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="16">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -1755,7 +1756,7 @@
     <numFmt numFmtId="175" formatCode="_(&quot;$&quot;* #,##0.0000_);_(&quot;$&quot;* \(#,##0.0000\);_(&quot;$&quot;* &quot;-&quot;????_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="50" x14ac:knownFonts="1">
+  <fonts count="50">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4077,36 +4078,36 @@
     </xf>
   </cellXfs>
   <cellStyles count="30">
-    <cellStyle name="Comma 2" xfId="5"/>
-    <cellStyle name="Comma 2 2" xfId="24"/>
-    <cellStyle name="Comma 2 2 2" xfId="29"/>
+    <cellStyle name="Comma 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Comma 2 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2 2 2" xfId="29" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Currency" xfId="20" builtinId="4"/>
-    <cellStyle name="Currency 2" xfId="4"/>
-    <cellStyle name="Currency 2 2" xfId="25"/>
-    <cellStyle name="Currency 3" xfId="8"/>
-    <cellStyle name="Currency 4" xfId="19"/>
-    <cellStyle name="Currency 5" xfId="16"/>
+    <cellStyle name="Currency 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Currency 2 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Currency 3" xfId="8" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Currency 4" xfId="19" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Currency 5" xfId="16" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="15"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 2" xfId="3"/>
-    <cellStyle name="Normal 2 2 2" xfId="10"/>
-    <cellStyle name="Normal 2 3" xfId="14"/>
-    <cellStyle name="Normal 2 4" xfId="23"/>
-    <cellStyle name="Normal 2 4 2" xfId="28"/>
-    <cellStyle name="Normal 2_Sheet1" xfId="21"/>
-    <cellStyle name="Normal 3" xfId="6"/>
-    <cellStyle name="Normal 3 2" xfId="9"/>
-    <cellStyle name="Normal 4" xfId="13"/>
-    <cellStyle name="Normal 4 2" xfId="27"/>
-    <cellStyle name="Normal 5" xfId="11"/>
-    <cellStyle name="Normal 6" xfId="22"/>
-    <cellStyle name="Normal 9" xfId="18"/>
+    <cellStyle name="Normal 10" xfId="15" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Normal 2 3" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Normal 2 4" xfId="23" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Normal 2 4 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Normal 2_Sheet1" xfId="21" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Normal 3 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Normal 4" xfId="13" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Normal 4 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Normal 5" xfId="11" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Normal 6" xfId="22" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Normal 9" xfId="18" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
-    <cellStyle name="Percent 2" xfId="7"/>
-    <cellStyle name="Percent 2 2" xfId="12"/>
-    <cellStyle name="Percent 2 2 2" xfId="26"/>
-    <cellStyle name="Percent 4" xfId="17"/>
+    <cellStyle name="Percent 2" xfId="7" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Percent 2 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Percent 2 2 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Percent 4" xfId="17" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4388,46 +4389,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BA36"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="11.65" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="10.53125" style="47" customWidth="1"/>
-    <col min="2" max="2" width="15.46484375" style="46" customWidth="1"/>
-    <col min="3" max="4" width="11.86328125" style="46" customWidth="1"/>
-    <col min="5" max="5" width="16.1328125" style="46" customWidth="1"/>
-    <col min="6" max="7" width="11.86328125" style="46" customWidth="1"/>
-    <col min="8" max="8" width="13.53125" style="46" customWidth="1"/>
-    <col min="9" max="10" width="11.86328125" style="46" customWidth="1"/>
-    <col min="11" max="11" width="13.53125" style="46" customWidth="1"/>
-    <col min="12" max="25" width="11.86328125" style="46" customWidth="1"/>
-    <col min="26" max="26" width="14.46484375" style="46" customWidth="1"/>
-    <col min="27" max="28" width="11.86328125" style="46" customWidth="1"/>
-    <col min="29" max="29" width="14.86328125" style="47" customWidth="1"/>
-    <col min="30" max="31" width="11.86328125" style="47" customWidth="1"/>
-    <col min="32" max="32" width="13.46484375" style="47" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="47" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="46" customWidth="1"/>
+    <col min="3" max="4" width="11.83203125" style="46" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" style="46" customWidth="1"/>
+    <col min="6" max="7" width="11.83203125" style="46" customWidth="1"/>
+    <col min="8" max="8" width="13.5" style="46" customWidth="1"/>
+    <col min="9" max="10" width="11.83203125" style="46" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="46" customWidth="1"/>
+    <col min="12" max="25" width="11.83203125" style="46" customWidth="1"/>
+    <col min="26" max="26" width="14.5" style="46" customWidth="1"/>
+    <col min="27" max="28" width="11.83203125" style="46" customWidth="1"/>
+    <col min="29" max="29" width="14.83203125" style="47" customWidth="1"/>
+    <col min="30" max="31" width="11.83203125" style="47" customWidth="1"/>
+    <col min="32" max="32" width="13.5" style="47" customWidth="1"/>
     <col min="33" max="33" width="12" style="47" customWidth="1"/>
-    <col min="34" max="34" width="9.53125" style="47" customWidth="1"/>
-    <col min="35" max="35" width="13.1328125" style="47" customWidth="1"/>
-    <col min="36" max="36" width="11.86328125" style="47" customWidth="1"/>
-    <col min="37" max="37" width="9.1328125" style="47"/>
-    <col min="38" max="38" width="13.1328125" style="47" customWidth="1"/>
-    <col min="39" max="39" width="11.86328125" style="47" customWidth="1"/>
-    <col min="40" max="40" width="9.1328125" style="47"/>
-    <col min="41" max="41" width="9.86328125" style="51" customWidth="1"/>
-    <col min="42" max="42" width="16.46484375" style="47" customWidth="1"/>
-    <col min="43" max="43" width="12.46484375" style="52" customWidth="1"/>
-    <col min="44" max="44" width="9.53125" style="47" customWidth="1"/>
-    <col min="45" max="45" width="13.86328125" style="52" customWidth="1"/>
-    <col min="46" max="46" width="11.1328125" style="52" customWidth="1"/>
-    <col min="47" max="47" width="8.53125" style="47" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="14.53125" style="47" customWidth="1"/>
-    <col min="49" max="49" width="12.53125" style="52" customWidth="1"/>
+    <col min="34" max="34" width="9.5" style="47" customWidth="1"/>
+    <col min="35" max="35" width="13.1640625" style="47" customWidth="1"/>
+    <col min="36" max="36" width="11.83203125" style="47" customWidth="1"/>
+    <col min="37" max="37" width="9.1640625" style="47"/>
+    <col min="38" max="38" width="13.1640625" style="47" customWidth="1"/>
+    <col min="39" max="39" width="11.83203125" style="47" customWidth="1"/>
+    <col min="40" max="40" width="9.1640625" style="47"/>
+    <col min="41" max="41" width="9.83203125" style="51" customWidth="1"/>
+    <col min="42" max="42" width="16.5" style="47" customWidth="1"/>
+    <col min="43" max="43" width="12.5" style="52" customWidth="1"/>
+    <col min="44" max="44" width="9.5" style="47" customWidth="1"/>
+    <col min="45" max="45" width="13.83203125" style="52" customWidth="1"/>
+    <col min="46" max="46" width="11.1640625" style="52" customWidth="1"/>
+    <col min="47" max="47" width="8.5" style="47" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="14.5" style="47" customWidth="1"/>
+    <col min="49" max="49" width="12.5" style="52" customWidth="1"/>
     <col min="50" max="50" width="10" style="51" customWidth="1"/>
-    <col min="51" max="16384" width="9.1328125" style="47"/>
+    <col min="51" max="16384" width="9.1640625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:52" ht="26.25" customHeight="1" thickBot="1">
       <c r="A1" s="227"/>
       <c r="B1" s="399" t="s">
         <v>168</v>
@@ -4511,7 +4512,7 @@
       <c r="AW1" s="400"/>
       <c r="AX1" s="401"/>
     </row>
-    <row r="2" spans="1:52" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:52" ht="18.75" customHeight="1" thickBot="1">
       <c r="A2" s="227"/>
       <c r="B2" s="202" t="s">
         <v>4</v>
@@ -4659,7 +4660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:52" s="48" customFormat="1" ht="27" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:52" s="48" customFormat="1" ht="27" customHeight="1" thickTop="1" thickBot="1">
       <c r="A3" s="227"/>
       <c r="B3" s="228">
         <v>1035354.15</v>
@@ -4807,7 +4808,7 @@
         <v>3.8685795381504004E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:52" s="48" customFormat="1" ht="35.65" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:52" s="48" customFormat="1" ht="41" thickTop="1" thickBot="1">
       <c r="A4" s="54" t="s">
         <v>7</v>
       </c>
@@ -4961,7 +4962,7 @@
       <c r="AY4" s="50"/>
       <c r="AZ4" s="50"/>
     </row>
-    <row r="5" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A5" s="35" t="s">
         <v>265</v>
       </c>
@@ -5043,7 +5044,7 @@
       <c r="AY5" s="49"/>
       <c r="AZ5" s="49"/>
     </row>
-    <row r="6" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A6" s="35" t="s">
         <v>20</v>
       </c>
@@ -5117,7 +5118,7 @@
       <c r="AY6" s="49"/>
       <c r="AZ6" s="49"/>
     </row>
-    <row r="7" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A7" s="36" t="s">
         <v>22</v>
       </c>
@@ -5259,7 +5260,7 @@
       <c r="AY7" s="49"/>
       <c r="AZ7" s="49"/>
     </row>
-    <row r="8" spans="1:52" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:52" s="48" customFormat="1" ht="13">
       <c r="A8" s="36" t="s">
         <v>23</v>
       </c>
@@ -5353,7 +5354,7 @@
       <c r="AY8" s="49"/>
       <c r="AZ8" s="49"/>
     </row>
-    <row r="9" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A9" s="36" t="s">
         <v>24</v>
       </c>
@@ -5507,7 +5508,7 @@
       <c r="AY9" s="49"/>
       <c r="AZ9" s="49"/>
     </row>
-    <row r="10" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A10" s="248" t="s">
         <v>27</v>
       </c>
@@ -5601,7 +5602,7 @@
       <c r="AY10" s="49"/>
       <c r="AZ10" s="49"/>
     </row>
-    <row r="11" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A11" s="36" t="s">
         <v>29</v>
       </c>
@@ -5703,7 +5704,7 @@
       <c r="AY11" s="49"/>
       <c r="AZ11" s="49"/>
     </row>
-    <row r="12" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A12" s="36" t="s">
         <v>31</v>
       </c>
@@ -5857,7 +5858,7 @@
       <c r="AY12" s="49"/>
       <c r="AZ12" s="49"/>
     </row>
-    <row r="13" spans="1:52" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:52" s="48" customFormat="1">
       <c r="A13" s="250" t="s">
         <v>33</v>
       </c>
@@ -5999,7 +6000,7 @@
       <c r="AY13" s="49"/>
       <c r="AZ13" s="49"/>
     </row>
-    <row r="14" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A14" s="36" t="s">
         <v>42</v>
       </c>
@@ -6153,7 +6154,7 @@
       <c r="AY14" s="49"/>
       <c r="AZ14" s="49"/>
     </row>
-    <row r="15" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A15" s="36" t="s">
         <v>45</v>
       </c>
@@ -6307,7 +6308,7 @@
       <c r="AY15" s="49"/>
       <c r="AZ15" s="49"/>
     </row>
-    <row r="16" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:52" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A16" s="36" t="s">
         <v>49</v>
       </c>
@@ -6431,7 +6432,7 @@
       <c r="AY16" s="49"/>
       <c r="AZ16" s="49"/>
     </row>
-    <row r="17" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A17" s="36" t="s">
         <v>54</v>
       </c>
@@ -6538,7 +6539,7 @@
       <c r="AZ17" s="49"/>
       <c r="BA17" s="34"/>
     </row>
-    <row r="18" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A18" s="36" t="s">
         <v>57</v>
       </c>
@@ -6692,7 +6693,7 @@
       <c r="AY18" s="49"/>
       <c r="AZ18" s="49"/>
     </row>
-    <row r="19" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A19" s="250" t="s">
         <v>68</v>
       </c>
@@ -6846,7 +6847,7 @@
       <c r="AY19" s="49"/>
       <c r="AZ19" s="49"/>
     </row>
-    <row r="20" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A20" s="250" t="s">
         <v>70</v>
       </c>
@@ -6930,7 +6931,7 @@
       <c r="AY20" s="49"/>
       <c r="AZ20" s="49"/>
     </row>
-    <row r="21" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A21" s="36" t="s">
         <v>71</v>
       </c>
@@ -7010,7 +7011,7 @@
       <c r="AY21" s="49"/>
       <c r="AZ21" s="49"/>
     </row>
-    <row r="22" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A22" s="36" t="s">
         <v>72</v>
       </c>
@@ -7164,7 +7165,7 @@
       <c r="AY22" s="49"/>
       <c r="AZ22" s="49"/>
     </row>
-    <row r="23" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A23" s="36" t="s">
         <v>73</v>
       </c>
@@ -7312,7 +7313,7 @@
       <c r="AY23" s="49"/>
       <c r="AZ23" s="49"/>
     </row>
-    <row r="24" spans="1:53" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:53" s="48" customFormat="1" ht="13">
       <c r="A24" s="36" t="s">
         <v>76</v>
       </c>
@@ -7466,7 +7467,7 @@
       <c r="AY24" s="49"/>
       <c r="AZ24" s="49"/>
     </row>
-    <row r="25" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A25" s="36" t="s">
         <v>82</v>
       </c>
@@ -7620,7 +7621,7 @@
       <c r="AY25" s="49"/>
       <c r="AZ25" s="49"/>
     </row>
-    <row r="26" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A26" s="36" t="s">
         <v>112</v>
       </c>
@@ -7694,7 +7695,7 @@
       <c r="AY26" s="49"/>
       <c r="AZ26" s="49"/>
     </row>
-    <row r="27" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A27" s="36" t="s">
         <v>85</v>
       </c>
@@ -7848,7 +7849,7 @@
       <c r="AY27" s="49"/>
       <c r="AZ27" s="49"/>
     </row>
-    <row r="28" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A28" s="36" t="s">
         <v>86</v>
       </c>
@@ -7964,7 +7965,7 @@
       <c r="AY28" s="49"/>
       <c r="AZ28" s="49"/>
     </row>
-    <row r="29" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1">
       <c r="A29" s="36" t="s">
         <v>87</v>
       </c>
@@ -8118,7 +8119,7 @@
       <c r="AY29" s="49"/>
       <c r="AZ29" s="49"/>
     </row>
-    <row r="30" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:53" s="48" customFormat="1" ht="12" customHeight="1" thickBot="1">
       <c r="A30" s="37" t="s">
         <v>88</v>
       </c>
@@ -8272,7 +8273,7 @@
       <c r="AY30" s="49"/>
       <c r="AZ30" s="49"/>
     </row>
-    <row r="31" spans="1:53" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:53">
       <c r="A31" s="253"/>
       <c r="B31" s="254"/>
       <c r="C31" s="254"/>
@@ -8326,18 +8327,13 @@
       <c r="AY31" s="49"/>
       <c r="AZ31" s="49"/>
     </row>
-    <row r="36" spans="35:38" x14ac:dyDescent="0.45">
+    <row r="36" spans="35:38">
       <c r="AI36" s="53"/>
       <c r="AL36" s="53"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AX30"/>
+  <autoFilter ref="A4:AX30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="16">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:P1"/>
     <mergeCell ref="AI1:AK1"/>
     <mergeCell ref="AP1:AR1"/>
     <mergeCell ref="AS1:AU1"/>
@@ -8349,6 +8345,11 @@
     <mergeCell ref="AC1:AE1"/>
     <mergeCell ref="AF1:AH1"/>
     <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:P1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="65" orientation="landscape" r:id="rId1"/>
@@ -8361,25 +8362,25 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.53125" style="40" customWidth="1"/>
+    <col min="1" max="1" width="27.5" style="40" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" style="40" customWidth="1"/>
-    <col min="3" max="3" width="16.46484375" style="40" customWidth="1"/>
-    <col min="4" max="4" width="16.53125" style="40" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="40" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="40" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" style="40" customWidth="1"/>
-    <col min="6" max="16384" width="9.1328125" style="40"/>
+    <col min="6" max="16384" width="9.1640625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="16">
       <c r="A1" s="60"/>
       <c r="C1" s="60"/>
       <c r="D1" s="60"/>
       <c r="E1" s="60"/>
     </row>
-    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" s="447" t="s">
         <v>522</v>
       </c>
@@ -8388,7 +8389,7 @@
       <c r="D2" s="447"/>
       <c r="E2" s="447"/>
     </row>
-    <row r="3" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" s="448" t="s">
         <v>116</v>
       </c>
@@ -8397,7 +8398,7 @@
       <c r="D3" s="448"/>
       <c r="E3" s="448"/>
     </row>
-    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="68">
       <c r="A4" s="61" t="s">
         <v>7</v>
       </c>
@@ -8414,7 +8415,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="17">
       <c r="A5" s="41" t="s">
         <v>22</v>
       </c>
@@ -8431,7 +8432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" ht="17">
       <c r="A6" s="41" t="s">
         <v>23</v>
       </c>
@@ -8448,7 +8449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" ht="17">
       <c r="A7" s="41" t="s">
         <v>103</v>
       </c>
@@ -8465,7 +8466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" ht="17">
       <c r="A8" s="41" t="s">
         <v>29</v>
       </c>
@@ -8482,7 +8483,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" ht="17">
       <c r="A9" s="41" t="s">
         <v>31</v>
       </c>
@@ -8499,7 +8500,7 @@
         <v>1229.08</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" ht="17">
       <c r="A10" s="41" t="s">
         <v>33</v>
       </c>
@@ -8516,7 +8517,7 @@
         <v>6.3121800000000006E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" ht="17">
       <c r="A11" s="41" t="s">
         <v>45</v>
       </c>
@@ -8533,7 +8534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" ht="17">
       <c r="A12" s="41" t="s">
         <v>49</v>
       </c>
@@ -8550,7 +8551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" ht="17">
       <c r="A13" s="41" t="s">
         <v>54</v>
       </c>
@@ -8567,7 +8568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" ht="17">
       <c r="A14" s="41" t="s">
         <v>57</v>
       </c>
@@ -8584,7 +8585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="17">
       <c r="A15" s="41" t="s">
         <v>68</v>
       </c>
@@ -8601,7 +8602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" ht="17">
       <c r="A16" s="41" t="s">
         <v>70</v>
       </c>
@@ -8618,7 +8619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" ht="17">
       <c r="A17" s="41" t="s">
         <v>76</v>
       </c>
@@ -8635,7 +8636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" ht="17">
       <c r="A18" s="41" t="s">
         <v>82</v>
       </c>
@@ -8652,7 +8653,7 @@
         <v>619.39999999999986</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" ht="17">
       <c r="A19" s="41" t="s">
         <v>112</v>
       </c>
@@ -8669,7 +8670,7 @@
         <v>5.62E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" ht="17">
       <c r="A20" s="41" t="s">
         <v>85</v>
       </c>
@@ -8686,7 +8687,7 @@
         <v>0.59524914000000007</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" ht="17">
       <c r="A21" s="41" t="s">
         <v>86</v>
       </c>
@@ -8703,7 +8704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" ht="17">
       <c r="A22" s="41" t="s">
         <v>87</v>
       </c>
@@ -8720,7 +8721,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" ht="17">
       <c r="A23" s="41" t="s">
         <v>88</v>
       </c>
@@ -8737,7 +8738,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" ht="17">
       <c r="A24" s="41" t="s">
         <v>233</v>
       </c>
@@ -8754,18 +8755,18 @@
         <v>1850.2807613199996</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5">
       <c r="A28" s="42"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5">
       <c r="B29" s="446"/>
       <c r="C29" s="446"/>
       <c r="D29" s="446"/>
       <c r="E29" s="446"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E24">
-    <sortState ref="A5:G94">
+  <autoFilter ref="A4:E24" xr:uid="{00000000-0009-0000-0000-000009000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:G94">
       <sortCondition ref="A4:A94"/>
     </sortState>
   </autoFilter>
@@ -8785,42 +8786,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD166"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" style="40"/>
-    <col min="2" max="2" width="36.46484375" style="40" customWidth="1"/>
-    <col min="3" max="3" width="13.46484375" style="40" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="40"/>
+    <col min="2" max="2" width="36.5" style="40" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="40" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="40" customWidth="1"/>
-    <col min="5" max="5" width="9.06640625" style="40"/>
-    <col min="6" max="6" width="13.46484375" style="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1328125" style="40" customWidth="1"/>
-    <col min="8" max="8" width="9.06640625" style="40"/>
-    <col min="9" max="9" width="13.53125" style="40" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.86328125" style="40" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.06640625" style="40"/>
+    <col min="5" max="5" width="9" style="40"/>
+    <col min="6" max="6" width="13.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" style="40" customWidth="1"/>
+    <col min="8" max="8" width="9" style="40"/>
+    <col min="9" max="9" width="13.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" style="40" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="40"/>
     <col min="12" max="12" width="16" style="40" customWidth="1"/>
-    <col min="13" max="13" width="14.1328125" style="40" customWidth="1"/>
+    <col min="13" max="13" width="14.1640625" style="40" customWidth="1"/>
     <col min="14" max="14" width="9.6640625" style="40" customWidth="1"/>
     <col min="15" max="15" width="17.33203125" style="40" customWidth="1"/>
-    <col min="16" max="16" width="13.46484375" style="40" customWidth="1"/>
-    <col min="17" max="17" width="9.06640625" style="40"/>
+    <col min="16" max="16" width="13.5" style="40" customWidth="1"/>
+    <col min="17" max="17" width="9" style="40"/>
     <col min="18" max="18" width="12" style="40" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.46484375" style="40" customWidth="1"/>
-    <col min="20" max="20" width="15.53125" style="387" customWidth="1"/>
+    <col min="19" max="19" width="11.5" style="40" customWidth="1"/>
+    <col min="20" max="20" width="15.5" style="387" customWidth="1"/>
     <col min="21" max="21" width="10.6640625" style="40" customWidth="1"/>
-    <col min="22" max="22" width="14.1328125" style="387" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.46484375" style="387" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1640625" style="387" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5" style="387" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9.6640625" style="394" customWidth="1"/>
-    <col min="25" max="25" width="11.53125" style="387" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.1328125" style="387" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.06640625" style="394"/>
-    <col min="28" max="28" width="11.53125" style="387" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.06640625" style="40"/>
+    <col min="25" max="25" width="11.5" style="387" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.1640625" style="387" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9" style="394"/>
+    <col min="28" max="28" width="11.5" style="387" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="31.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:30" ht="31.25" customHeight="1" thickBot="1">
       <c r="A1" s="402"/>
       <c r="B1" s="403"/>
       <c r="C1" s="399" t="s">
@@ -8868,7 +8869,7 @@
       <c r="AC1" s="222"/>
       <c r="AD1" s="222"/>
     </row>
-    <row r="2" spans="1:30" ht="43.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:30" ht="43.25" customHeight="1" thickBot="1">
       <c r="A2" s="402"/>
       <c r="B2" s="403"/>
       <c r="C2" s="202" t="s">
@@ -8948,7 +8949,7 @@
       <c r="AC2" s="222"/>
       <c r="AD2" s="222"/>
     </row>
-    <row r="3" spans="1:30" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:30" ht="16" thickTop="1">
       <c r="A3" s="210"/>
       <c r="B3" s="209" t="s">
         <v>266</v>
@@ -9030,7 +9031,7 @@
       <c r="AC3" s="226"/>
       <c r="AD3" s="226"/>
     </row>
-    <row r="4" spans="1:30" ht="55.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:30" ht="59">
       <c r="A4" s="82" t="s">
         <v>7</v>
       </c>
@@ -9122,7 +9123,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:30">
       <c r="A5" s="86" t="s">
         <v>265</v>
       </c>
@@ -9190,7 +9191,7 @@
         <v>42583</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:30">
       <c r="A6" s="86" t="s">
         <v>20</v>
       </c>
@@ -9244,7 +9245,7 @@
       <c r="AC6" s="166"/>
       <c r="AD6" s="166"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:30">
       <c r="A7" s="86" t="s">
         <v>22</v>
       </c>
@@ -9318,7 +9319,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:30">
       <c r="A8" s="86" t="s">
         <v>22</v>
       </c>
@@ -9370,7 +9371,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:30">
       <c r="A9" s="86" t="s">
         <v>22</v>
       </c>
@@ -9462,7 +9463,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:30">
       <c r="A10" s="86" t="s">
         <v>22</v>
       </c>
@@ -9510,7 +9511,7 @@
       <c r="AC10" s="88"/>
       <c r="AD10" s="88"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:30">
       <c r="A11" s="86" t="s">
         <v>22</v>
       </c>
@@ -9552,7 +9553,7 @@
       <c r="AC11" s="88"/>
       <c r="AD11" s="88"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:30">
       <c r="A12" s="86" t="s">
         <v>22</v>
       </c>
@@ -9626,7 +9627,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:30">
       <c r="A13" s="86" t="s">
         <v>22</v>
       </c>
@@ -9674,7 +9675,7 @@
       <c r="AC13" s="88"/>
       <c r="AD13" s="88"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:30">
       <c r="A14" s="86" t="s">
         <v>22</v>
       </c>
@@ -9766,7 +9767,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:30">
       <c r="A15" s="86" t="s">
         <v>22</v>
       </c>
@@ -9840,7 +9841,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:30">
       <c r="A16" s="86" t="s">
         <v>22</v>
       </c>
@@ -9892,7 +9893,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:30">
       <c r="A17" s="86" t="s">
         <v>22</v>
       </c>
@@ -9984,7 +9985,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:30">
       <c r="A18" s="86" t="s">
         <v>22</v>
       </c>
@@ -10036,7 +10037,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:30">
       <c r="A19" s="86" t="s">
         <v>22</v>
       </c>
@@ -10128,7 +10129,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:30">
       <c r="A20" s="86" t="s">
         <v>22</v>
       </c>
@@ -10202,7 +10203,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:30">
       <c r="A21" s="86" t="s">
         <v>22</v>
       </c>
@@ -10294,7 +10295,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:30">
       <c r="A22" s="86" t="s">
         <v>22</v>
       </c>
@@ -10386,7 +10387,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:30">
       <c r="A23" s="86" t="s">
         <v>22</v>
       </c>
@@ -10478,7 +10479,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:30">
       <c r="A24" s="86" t="s">
         <v>22</v>
       </c>
@@ -10532,7 +10533,7 @@
       <c r="AC24" s="88"/>
       <c r="AD24" s="88"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:30">
       <c r="A25" s="86" t="s">
         <v>22</v>
       </c>
@@ -10574,7 +10575,7 @@
       <c r="AC25" s="88"/>
       <c r="AD25" s="88"/>
     </row>
-    <row r="26" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:30" ht="24">
       <c r="A26" s="86" t="s">
         <v>22</v>
       </c>
@@ -10616,7 +10617,7 @@
       <c r="AC26" s="88"/>
       <c r="AD26" s="88"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:30">
       <c r="A27" s="86" t="s">
         <v>22</v>
       </c>
@@ -10658,7 +10659,7 @@
       <c r="AC27" s="88"/>
       <c r="AD27" s="88"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:30">
       <c r="A28" s="86" t="s">
         <v>22</v>
       </c>
@@ -10750,7 +10751,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:30">
       <c r="A29" s="86" t="s">
         <v>22</v>
       </c>
@@ -10792,7 +10793,7 @@
       <c r="AC29" s="88"/>
       <c r="AD29" s="88"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:30">
       <c r="A30" s="86" t="s">
         <v>22</v>
       </c>
@@ -10844,7 +10845,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:30">
       <c r="A31" s="86" t="s">
         <v>22</v>
       </c>
@@ -10912,7 +10913,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:30">
       <c r="A32" s="86" t="s">
         <v>22</v>
       </c>
@@ -10986,7 +10987,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:30">
       <c r="A33" s="86" t="s">
         <v>22</v>
       </c>
@@ -11028,7 +11029,7 @@
       <c r="AC33" s="88"/>
       <c r="AD33" s="88"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:30">
       <c r="A34" s="86" t="s">
         <v>22</v>
       </c>
@@ -11108,7 +11109,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:30" ht="24">
       <c r="A35" s="86" t="s">
         <v>23</v>
       </c>
@@ -11188,7 +11189,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:30">
       <c r="A36" s="86" t="s">
         <v>24</v>
       </c>
@@ -11280,7 +11281,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:30">
       <c r="A37" s="86" t="s">
         <v>24</v>
       </c>
@@ -11366,7 +11367,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:30">
       <c r="A38" s="86" t="s">
         <v>24</v>
       </c>
@@ -11458,7 +11459,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="39" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:30" ht="24">
       <c r="A39" s="86" t="s">
         <v>24</v>
       </c>
@@ -11550,7 +11551,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:30">
       <c r="A40" s="86" t="s">
         <v>24</v>
       </c>
@@ -11642,7 +11643,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="41" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:30" ht="24">
       <c r="A41" s="86" t="s">
         <v>24</v>
       </c>
@@ -11734,7 +11735,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:30">
       <c r="A42" s="86" t="s">
         <v>24</v>
       </c>
@@ -11820,7 +11821,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="43" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:30" ht="24">
       <c r="A43" s="86" t="s">
         <v>24</v>
       </c>
@@ -11906,7 +11907,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="44" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:30" ht="24">
       <c r="A44" s="86" t="s">
         <v>24</v>
       </c>
@@ -11998,7 +11999,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:30">
       <c r="A45" s="102" t="s">
         <v>27</v>
       </c>
@@ -12078,7 +12079,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="46" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:30" ht="24">
       <c r="A46" s="86" t="s">
         <v>29</v>
       </c>
@@ -12158,7 +12159,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="47" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:30" ht="24">
       <c r="A47" s="86" t="s">
         <v>29</v>
       </c>
@@ -12238,7 +12239,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:30">
       <c r="A48" s="102" t="s">
         <v>31</v>
       </c>
@@ -12318,7 +12319,7 @@
         <v>42551</v>
       </c>
     </row>
-    <row r="49" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:30" ht="24">
       <c r="A49" s="102" t="s">
         <v>31</v>
       </c>
@@ -12360,7 +12361,7 @@
       <c r="AC49" s="88"/>
       <c r="AD49" s="88"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:30">
       <c r="A50" s="86" t="s">
         <v>31</v>
       </c>
@@ -12452,7 +12453,7 @@
         <v>42551</v>
       </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:30">
       <c r="A51" s="86" t="s">
         <v>31</v>
       </c>
@@ -12512,7 +12513,7 @@
       <c r="AC51" s="88"/>
       <c r="AD51" s="88"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:30">
       <c r="A52" s="86" t="s">
         <v>33</v>
       </c>
@@ -12572,7 +12573,7 @@
       <c r="AC52" s="88"/>
       <c r="AD52" s="88"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:30">
       <c r="A53" s="102" t="s">
         <v>33</v>
       </c>
@@ -12652,7 +12653,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:30">
       <c r="A54" s="102" t="s">
         <v>33</v>
       </c>
@@ -12694,7 +12695,7 @@
       <c r="AC54" s="88"/>
       <c r="AD54" s="88"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:30">
       <c r="A55" s="86" t="s">
         <v>33</v>
       </c>
@@ -12786,7 +12787,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:30">
       <c r="A56" s="102" t="s">
         <v>33</v>
       </c>
@@ -12860,7 +12861,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:30">
       <c r="A57" s="102" t="s">
         <v>33</v>
       </c>
@@ -12902,7 +12903,7 @@
       <c r="AC57" s="88"/>
       <c r="AD57" s="88"/>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:30">
       <c r="A58" s="102" t="s">
         <v>33</v>
       </c>
@@ -12982,7 +12983,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:30">
       <c r="A59" s="86" t="s">
         <v>33</v>
       </c>
@@ -13036,7 +13037,7 @@
       <c r="AC59" s="88"/>
       <c r="AD59" s="88"/>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:30">
       <c r="A60" s="102" t="s">
         <v>33</v>
       </c>
@@ -13116,7 +13117,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:30">
       <c r="A61" s="86" t="s">
         <v>33</v>
       </c>
@@ -13208,7 +13209,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:30">
       <c r="A62" s="102" t="s">
         <v>33</v>
       </c>
@@ -13282,7 +13283,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:30">
       <c r="A63" s="86" t="s">
         <v>33</v>
       </c>
@@ -13350,7 +13351,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:30">
       <c r="A64" s="86" t="s">
         <v>42</v>
       </c>
@@ -13436,7 +13437,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:30">
       <c r="A65" s="86" t="s">
         <v>42</v>
       </c>
@@ -13484,7 +13485,7 @@
       <c r="AC65" s="88"/>
       <c r="AD65" s="88"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:30">
       <c r="A66" s="86" t="s">
         <v>42</v>
       </c>
@@ -13576,7 +13577,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:30">
       <c r="A67" s="86" t="s">
         <v>42</v>
       </c>
@@ -13636,7 +13637,7 @@
       <c r="AC67" s="88"/>
       <c r="AD67" s="88"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:30">
       <c r="A68" s="86" t="s">
         <v>45</v>
       </c>
@@ -13678,7 +13679,7 @@
       <c r="AC68" s="88"/>
       <c r="AD68" s="88"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:30">
       <c r="A69" s="86" t="s">
         <v>45</v>
       </c>
@@ -13764,7 +13765,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:30">
       <c r="A70" s="86" t="s">
         <v>45</v>
       </c>
@@ -13850,7 +13851,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:30">
       <c r="A71" s="86" t="s">
         <v>45</v>
       </c>
@@ -13930,7 +13931,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="72" spans="1:30" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:30" ht="16" thickBot="1">
       <c r="A72" s="86" t="s">
         <v>49</v>
       </c>
@@ -14022,7 +14023,7 @@
         <v>42551</v>
       </c>
     </row>
-    <row r="73" spans="1:30" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:30" ht="16" thickBot="1">
       <c r="A73" s="86" t="s">
         <v>49</v>
       </c>
@@ -14114,7 +14115,7 @@
         <v>42369</v>
       </c>
     </row>
-    <row r="74" spans="1:30" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:30" ht="16" thickBot="1">
       <c r="A74" s="86" t="s">
         <v>49</v>
       </c>
@@ -14194,7 +14195,7 @@
         <v>42369</v>
       </c>
     </row>
-    <row r="75" spans="1:30" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:30" ht="16" thickBot="1">
       <c r="A75" s="86" t="s">
         <v>49</v>
       </c>
@@ -14286,7 +14287,7 @@
         <v>42369</v>
       </c>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:30">
       <c r="A76" s="86" t="s">
         <v>54</v>
       </c>
@@ -14340,7 +14341,7 @@
       <c r="AC76" s="96"/>
       <c r="AD76" s="96"/>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:30">
       <c r="A77" s="102" t="s">
         <v>54</v>
       </c>
@@ -14420,7 +14421,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:30">
       <c r="A78" s="86" t="s">
         <v>54</v>
       </c>
@@ -14468,7 +14469,7 @@
       <c r="AC78" s="88"/>
       <c r="AD78" s="88"/>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:30">
       <c r="A79" s="86" t="s">
         <v>54</v>
       </c>
@@ -14516,7 +14517,7 @@
       <c r="AC79" s="88"/>
       <c r="AD79" s="88"/>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:30">
       <c r="A80" s="86" t="s">
         <v>54</v>
       </c>
@@ -14602,7 +14603,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:30">
       <c r="A81" s="86" t="s">
         <v>54</v>
       </c>
@@ -14688,7 +14689,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:30">
       <c r="A82" s="102" t="s">
         <v>57</v>
       </c>
@@ -14736,7 +14737,7 @@
       <c r="AC82" s="88"/>
       <c r="AD82" s="88"/>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:30">
       <c r="A83" s="163" t="s">
         <v>57</v>
       </c>
@@ -14810,7 +14811,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:30">
       <c r="A84" s="102" t="s">
         <v>57</v>
       </c>
@@ -14878,7 +14879,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:30">
       <c r="A85" s="102" t="s">
         <v>57</v>
       </c>
@@ -14940,7 +14941,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:30">
       <c r="A86" s="102" t="s">
         <v>57</v>
       </c>
@@ -14988,7 +14989,7 @@
       <c r="AC86" s="88"/>
       <c r="AD86" s="88"/>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:30">
       <c r="A87" s="86" t="s">
         <v>57</v>
       </c>
@@ -15080,7 +15081,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:30">
       <c r="A88" s="86" t="s">
         <v>57</v>
       </c>
@@ -15172,7 +15173,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:30">
       <c r="A89" s="86" t="s">
         <v>57</v>
       </c>
@@ -15264,7 +15265,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:30">
       <c r="A90" s="86" t="s">
         <v>57</v>
       </c>
@@ -15356,7 +15357,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:30">
       <c r="A91" s="86" t="s">
         <v>57</v>
       </c>
@@ -15448,7 +15449,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:30">
       <c r="A92" s="86" t="s">
         <v>57</v>
       </c>
@@ -15540,7 +15541,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:30">
       <c r="A93" s="86" t="s">
         <v>57</v>
       </c>
@@ -15632,7 +15633,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:30">
       <c r="A94" s="102" t="s">
         <v>57</v>
       </c>
@@ -15694,7 +15695,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:30">
       <c r="A95" s="102" t="s">
         <v>57</v>
       </c>
@@ -15756,7 +15757,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="96" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:30" ht="24">
       <c r="A96" s="102" t="s">
         <v>68</v>
       </c>
@@ -15836,7 +15837,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="97" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:30" ht="24">
       <c r="A97" s="86" t="s">
         <v>68</v>
       </c>
@@ -15928,7 +15929,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:30">
       <c r="A98" s="102" t="s">
         <v>70</v>
       </c>
@@ -16000,7 +16001,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:30">
       <c r="A99" s="86" t="s">
         <v>71</v>
       </c>
@@ -16042,7 +16043,7 @@
       <c r="AC99" s="88"/>
       <c r="AD99" s="88"/>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:30">
       <c r="A100" s="86" t="s">
         <v>72</v>
       </c>
@@ -16084,7 +16085,7 @@
       <c r="AC100" s="88"/>
       <c r="AD100" s="88"/>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:30">
       <c r="A101" s="86" t="s">
         <v>72</v>
       </c>
@@ -16126,7 +16127,7 @@
       <c r="AC101" s="88"/>
       <c r="AD101" s="88"/>
     </row>
-    <row r="102" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:30" ht="24">
       <c r="A102" s="86" t="s">
         <v>72</v>
       </c>
@@ -16218,7 +16219,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="103" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:30" ht="24">
       <c r="A103" s="86" t="s">
         <v>72</v>
       </c>
@@ -16310,7 +16311,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:30">
       <c r="A104" s="86" t="s">
         <v>73</v>
       </c>
@@ -16402,7 +16403,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:30">
       <c r="A105" s="86" t="s">
         <v>73</v>
       </c>
@@ -16482,7 +16483,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:30">
       <c r="A106" s="86" t="s">
         <v>76</v>
       </c>
@@ -16574,7 +16575,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:30">
       <c r="A107" s="86" t="s">
         <v>76</v>
       </c>
@@ -16666,7 +16667,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:30">
       <c r="A108" s="86" t="s">
         <v>76</v>
       </c>
@@ -16758,7 +16759,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:30">
       <c r="A109" s="86" t="s">
         <v>76</v>
       </c>
@@ -16850,7 +16851,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:30">
       <c r="A110" s="86" t="s">
         <v>76</v>
       </c>
@@ -16942,7 +16943,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="111" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:30" ht="24">
       <c r="A111" s="86" t="s">
         <v>76</v>
       </c>
@@ -17016,7 +17017,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="112" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:30" ht="24">
       <c r="A112" s="86" t="s">
         <v>76</v>
       </c>
@@ -17090,7 +17091,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="113" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:30" ht="24">
       <c r="A113" s="86" t="s">
         <v>76</v>
       </c>
@@ -17164,7 +17165,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="114" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:30">
       <c r="A114" s="102" t="s">
         <v>76</v>
       </c>
@@ -17244,7 +17245,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="115" spans="1:30" ht="21.4" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:30" ht="25">
       <c r="A115" s="86" t="s">
         <v>82</v>
       </c>
@@ -17324,7 +17325,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="116" spans="1:30" ht="21.4" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:30" ht="25">
       <c r="A116" s="86" t="s">
         <v>82</v>
       </c>
@@ -17416,7 +17417,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="117" spans="1:30" ht="21.4" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:30" ht="25">
       <c r="A117" s="86" t="s">
         <v>82</v>
       </c>
@@ -17508,7 +17509,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="118" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:30">
       <c r="A118" s="86" t="s">
         <v>85</v>
       </c>
@@ -17598,7 +17599,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="119" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:30">
       <c r="A119" s="86" t="s">
         <v>86</v>
       </c>
@@ -17652,7 +17653,7 @@
       <c r="AC119" s="88"/>
       <c r="AD119" s="88"/>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:30">
       <c r="A120" s="86" t="s">
         <v>87</v>
       </c>
@@ -17700,7 +17701,7 @@
       <c r="AC120" s="88"/>
       <c r="AD120" s="88"/>
     </row>
-    <row r="121" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:30">
       <c r="A121" s="86" t="s">
         <v>87</v>
       </c>
@@ -17774,7 +17775,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="122" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:30">
       <c r="A122" s="102" t="s">
         <v>87</v>
       </c>
@@ -17816,7 +17817,7 @@
       <c r="AC122" s="88"/>
       <c r="AD122" s="88"/>
     </row>
-    <row r="123" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:30">
       <c r="A123" s="86" t="s">
         <v>87</v>
       </c>
@@ -17908,7 +17909,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="124" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:30">
       <c r="A124" s="86" t="s">
         <v>87</v>
       </c>
@@ -18000,7 +18001,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="125" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:30" ht="24">
       <c r="A125" s="86" t="s">
         <v>87</v>
       </c>
@@ -18092,7 +18093,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="126" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:30">
       <c r="A126" s="86" t="s">
         <v>87</v>
       </c>
@@ -18152,7 +18153,7 @@
       <c r="AC126" s="88"/>
       <c r="AD126" s="88"/>
     </row>
-    <row r="127" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:30" ht="24">
       <c r="A127" s="102" t="s">
         <v>87</v>
       </c>
@@ -18232,7 +18233,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="128" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:30">
       <c r="A128" s="102" t="s">
         <v>87</v>
       </c>
@@ -18306,7 +18307,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="129" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:30">
       <c r="A129" s="86" t="s">
         <v>87</v>
       </c>
@@ -18360,7 +18361,7 @@
       <c r="AC129" s="88"/>
       <c r="AD129" s="88"/>
     </row>
-    <row r="130" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:30">
       <c r="A130" s="86" t="s">
         <v>87</v>
       </c>
@@ -18408,7 +18409,7 @@
       <c r="AC130" s="88"/>
       <c r="AD130" s="88"/>
     </row>
-    <row r="131" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:30" ht="24">
       <c r="A131" s="102" t="s">
         <v>87</v>
       </c>
@@ -18488,7 +18489,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="132" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:30" ht="24">
       <c r="A132" s="86" t="s">
         <v>87</v>
       </c>
@@ -18562,7 +18563,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="133" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:30">
       <c r="A133" s="86" t="s">
         <v>87</v>
       </c>
@@ -18636,7 +18637,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="134" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:30">
       <c r="A134" s="86" t="s">
         <v>87</v>
       </c>
@@ -18710,7 +18711,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="135" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:30">
       <c r="A135" s="102" t="s">
         <v>87</v>
       </c>
@@ -18784,7 +18785,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="136" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:30">
       <c r="A136" s="86" t="s">
         <v>87</v>
       </c>
@@ -18832,7 +18833,7 @@
       <c r="AC136" s="88"/>
       <c r="AD136" s="88"/>
     </row>
-    <row r="137" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:30">
       <c r="A137" s="86" t="s">
         <v>87</v>
       </c>
@@ -18924,7 +18925,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="138" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:30" ht="24">
       <c r="A138" s="102" t="s">
         <v>87</v>
       </c>
@@ -19016,7 +19017,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="139" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:30">
       <c r="A139" s="86" t="s">
         <v>87</v>
       </c>
@@ -19064,7 +19065,7 @@
       <c r="AC139" s="88"/>
       <c r="AD139" s="88"/>
     </row>
-    <row r="140" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:30" ht="24">
       <c r="A140" s="86" t="s">
         <v>87</v>
       </c>
@@ -19156,7 +19157,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="141" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:30" ht="24">
       <c r="A141" s="102" t="s">
         <v>87</v>
       </c>
@@ -19230,7 +19231,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="142" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:30">
       <c r="A142" s="86" t="s">
         <v>87</v>
       </c>
@@ -19322,7 +19323,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="143" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:30" ht="24">
       <c r="A143" s="86" t="s">
         <v>87</v>
       </c>
@@ -19414,7 +19415,7 @@
         <v>41791</v>
       </c>
     </row>
-    <row r="144" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:30" ht="24">
       <c r="A144" s="86" t="s">
         <v>88</v>
       </c>
@@ -19500,7 +19501,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="145" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:30" ht="24">
       <c r="A145" s="86" t="s">
         <v>88</v>
       </c>
@@ -19592,7 +19593,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="146" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:30" ht="24">
       <c r="A146" s="86" t="s">
         <v>88</v>
       </c>
@@ -19678,7 +19679,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="147" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:30">
       <c r="A147" s="86" t="s">
         <v>88</v>
       </c>
@@ -19720,7 +19721,7 @@
       <c r="AC147" s="88"/>
       <c r="AD147" s="88"/>
     </row>
-    <row r="148" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:30" ht="24">
       <c r="A148" s="86" t="s">
         <v>88</v>
       </c>
@@ -19800,7 +19801,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="149" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:30">
       <c r="A149" s="86" t="s">
         <v>88</v>
       </c>
@@ -19842,7 +19843,7 @@
       <c r="AC149" s="88"/>
       <c r="AD149" s="88"/>
     </row>
-    <row r="150" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:30" ht="24">
       <c r="A150" s="86" t="s">
         <v>88</v>
       </c>
@@ -19928,7 +19929,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="151" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:30" ht="24">
       <c r="A151" s="86" t="s">
         <v>88</v>
       </c>
@@ -20014,7 +20015,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="152" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:30" ht="24">
       <c r="A152" s="86" t="s">
         <v>88</v>
       </c>
@@ -20100,7 +20101,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="153" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:30">
       <c r="A153" s="86" t="s">
         <v>88</v>
       </c>
@@ -20148,7 +20149,7 @@
       <c r="AC153" s="88"/>
       <c r="AD153" s="88"/>
     </row>
-    <row r="154" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:30" ht="24">
       <c r="A154" s="86" t="s">
         <v>88</v>
       </c>
@@ -20234,7 +20235,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="155" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:30" ht="24">
       <c r="A155" s="102" t="s">
         <v>88</v>
       </c>
@@ -20314,7 +20315,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="156" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:30" ht="24">
       <c r="A156" s="102" t="s">
         <v>88</v>
       </c>
@@ -20394,7 +20395,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="157" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:30" ht="24">
       <c r="A157" s="86" t="s">
         <v>88</v>
       </c>
@@ -20486,7 +20487,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="158" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:30" ht="24">
       <c r="A158" s="86" t="s">
         <v>88</v>
       </c>
@@ -20578,7 +20579,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="159" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:30" ht="24">
       <c r="A159" s="102" t="s">
         <v>88</v>
       </c>
@@ -20658,7 +20659,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="160" spans="1:30" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:30" ht="24">
       <c r="A160" s="86" t="s">
         <v>88</v>
       </c>
@@ -20750,7 +20751,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="161" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:30">
       <c r="A161" s="222"/>
       <c r="B161" s="222"/>
       <c r="C161" s="223"/>
@@ -20782,7 +20783,7 @@
       <c r="AC161" s="222"/>
       <c r="AD161" s="222"/>
     </row>
-    <row r="162" spans="1:30" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:30" ht="16" thickBot="1">
       <c r="A162" s="106"/>
       <c r="B162" s="218" t="s">
         <v>252</v>
@@ -20850,17 +20851,17 @@
       <c r="AC162" s="81"/>
       <c r="AD162" s="81"/>
     </row>
-    <row r="163" spans="1:30" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="165" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:30" ht="16" thickTop="1"/>
+    <row r="165" spans="1:30">
       <c r="L165" s="221"/>
       <c r="M165" s="221"/>
     </row>
-    <row r="166" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:30">
       <c r="D166" s="221"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AD160">
-    <sortState ref="A5:AD160">
+  <autoFilter ref="A4:AD160" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AD160">
       <sortCondition ref="A4:A160"/>
     </sortState>
   </autoFilter>
@@ -20886,9 +20887,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AY23"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="11.65" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="47" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" style="47" customWidth="1"/>
@@ -20896,26 +20897,26 @@
     <col min="30" max="32" width="13" style="47" customWidth="1"/>
     <col min="33" max="33" width="13" style="47" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="13" style="47" customWidth="1"/>
-    <col min="35" max="35" width="10.53125" style="47" customWidth="1"/>
-    <col min="36" max="36" width="13.1328125" style="47" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.5" style="47" customWidth="1"/>
+    <col min="36" max="36" width="13.1640625" style="47" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="13" style="47" customWidth="1"/>
     <col min="38" max="38" width="8.6640625" style="47"/>
-    <col min="39" max="39" width="13.1328125" style="47" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.1640625" style="47" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="13" style="47" customWidth="1"/>
     <col min="41" max="42" width="8.6640625" style="47"/>
-    <col min="43" max="43" width="11.1328125" style="51" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="10.53125" style="51" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.1640625" style="51" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="10.5" style="51" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="8.6640625" style="51"/>
-    <col min="46" max="46" width="11.1328125" style="51" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="10.53125" style="51" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11.1640625" style="51" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="10.5" style="51" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="8.6640625" style="51"/>
-    <col min="49" max="49" width="11.1328125" style="51" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="10.53125" style="51" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="11.1640625" style="51" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.5" style="51" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="8.6640625" style="51"/>
     <col min="52" max="16384" width="8.6640625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="64" customFormat="1" ht="34.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:51" s="64" customFormat="1" ht="39">
       <c r="A1" s="70" t="s">
         <v>7</v>
       </c>
@@ -21068,7 +21069,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="2" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A2" s="65" t="s">
         <v>57</v>
       </c>
@@ -21221,7 +21222,7 @@
         <v>9.3000011098655952E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A3" s="65" t="s">
         <v>57</v>
       </c>
@@ -21350,7 +21351,7 @@
         <v>5.5099990080907629E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A4" s="65" t="s">
         <v>85</v>
       </c>
@@ -21503,7 +21504,7 @@
         <v>0.24019993774558274</v>
       </c>
     </row>
-    <row r="5" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A5" s="65" t="s">
         <v>57</v>
       </c>
@@ -21632,7 +21633,7 @@
         <v>9.0999987277515557E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A6" s="65" t="s">
         <v>82</v>
       </c>
@@ -21785,7 +21786,7 @@
         <v>6.2000035998257146E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A7" s="65" t="s">
         <v>42</v>
       </c>
@@ -21884,7 +21885,7 @@
         <v>3.9800025336156508E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A8" s="65" t="s">
         <v>31</v>
       </c>
@@ -22037,7 +22038,7 @@
         <v>0.1135</v>
       </c>
     </row>
-    <row r="9" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A9" s="65" t="s">
         <v>82</v>
       </c>
@@ -22190,7 +22191,7 @@
         <v>4.0000037309444649E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:51" s="64" customFormat="1">
       <c r="A10" s="68" t="s">
         <v>88</v>
       </c>
@@ -22283,7 +22284,7 @@
         <v>0.71000009675952358</v>
       </c>
     </row>
-    <row r="11" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A11" s="65" t="s">
         <v>57</v>
       </c>
@@ -22394,7 +22395,7 @@
         <v>3.1999964649321269E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A12" s="65" t="s">
         <v>42</v>
       </c>
@@ -22547,7 +22548,7 @@
         <v>7.8500065728933879E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A13" s="65" t="s">
         <v>87</v>
       </c>
@@ -22682,7 +22683,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A14" s="65" t="s">
         <v>68</v>
       </c>
@@ -22835,7 +22836,7 @@
         <v>4.8979989511727225E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:51" s="64" customFormat="1">
       <c r="A15" s="68" t="s">
         <v>88</v>
       </c>
@@ -22928,7 +22929,7 @@
         <v>0.64999785380091857</v>
       </c>
     </row>
-    <row r="16" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A16" s="65" t="s">
         <v>87</v>
       </c>
@@ -23063,7 +23064,7 @@
         <v>0.20065426555484286</v>
       </c>
     </row>
-    <row r="17" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A17" s="65" t="s">
         <v>57</v>
       </c>
@@ -23174,7 +23175,7 @@
         <v>6.2399818283455255E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A18" s="65" t="s">
         <v>88</v>
       </c>
@@ -23273,7 +23274,7 @@
         <v>5.2999611981297406E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A19" s="65" t="s">
         <v>87</v>
       </c>
@@ -23426,7 +23427,7 @@
         <v>1.9900126422250315E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A20" s="65" t="s">
         <v>76</v>
       </c>
@@ -23555,7 +23556,7 @@
         <v>3.7000148017192133E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:51" s="64" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:51" s="64" customFormat="1" ht="13">
       <c r="A21" s="65" t="s">
         <v>87</v>
       </c>
@@ -23684,7 +23685,7 @@
       <c r="AX21" s="129"/>
       <c r="AY21" s="129"/>
     </row>
-    <row r="22" spans="1:51" s="63" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:51" s="63" customFormat="1">
       <c r="C22" s="133"/>
       <c r="D22" s="69"/>
       <c r="E22" s="134"/>
@@ -23733,7 +23734,7 @@
       <c r="AX22" s="51"/>
       <c r="AY22" s="149"/>
     </row>
-    <row r="23" spans="1:51" s="63" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:51" s="63" customFormat="1" ht="13" thickBot="1">
       <c r="A23" s="260"/>
       <c r="B23" s="287" t="s">
         <v>518</v>
@@ -23885,8 +23886,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AY21">
-    <sortState ref="A2:AY21">
+  <autoFilter ref="A1:AY21" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AY21">
       <sortCondition descending="1" ref="AN1:AN21"/>
     </sortState>
   </autoFilter>
@@ -23901,22 +23902,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.86328125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="16.53125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="15.53125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="16.53125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="14.86328125" style="21" customWidth="1"/>
-    <col min="6" max="7" width="16.46484375" style="21" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="21" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" style="21" customWidth="1"/>
+    <col min="6" max="7" width="16.5" style="21" customWidth="1"/>
     <col min="8" max="8" width="9" style="5" customWidth="1"/>
     <col min="9" max="9" width="6.33203125" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="9.1328125" style="5"/>
+    <col min="10" max="16384" width="9.1640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="407" t="s">
         <v>153</v>
       </c>
@@ -23927,7 +23928,7 @@
       <c r="F1" s="407"/>
       <c r="G1" s="407"/>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="15" customHeight="1">
       <c r="A2" s="408"/>
       <c r="B2" s="408"/>
       <c r="C2" s="408"/>
@@ -23936,7 +23937,7 @@
       <c r="F2" s="408"/>
       <c r="G2" s="408"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" ht="16">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
@@ -23959,7 +23960,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" ht="16">
       <c r="A4" s="8" t="s">
         <v>22</v>
       </c>
@@ -23980,7 +23981,7 @@
       </c>
       <c r="G4" s="10"/>
     </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>23</v>
       </c>
@@ -24002,7 +24003,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="11"/>
     </row>
-    <row r="6" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" ht="18.75" customHeight="1">
       <c r="A6" s="12" t="s">
         <v>24</v>
       </c>
@@ -24023,7 +24024,7 @@
       </c>
       <c r="G6" s="10"/>
     </row>
-    <row r="7" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" ht="17.25" customHeight="1">
       <c r="A7" s="12" t="s">
         <v>103</v>
       </c>
@@ -24044,7 +24045,7 @@
       </c>
       <c r="G7" s="10"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" ht="16">
       <c r="A8" s="12" t="s">
         <v>27</v>
       </c>
@@ -24066,7 +24067,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" ht="16">
       <c r="A9" s="12" t="s">
         <v>29</v>
       </c>
@@ -24087,7 +24088,7 @@
       </c>
       <c r="G9" s="10"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" ht="16">
       <c r="A10" s="12" t="s">
         <v>31</v>
       </c>
@@ -24108,7 +24109,7 @@
       </c>
       <c r="G10" s="10"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" ht="16">
       <c r="A11" s="12" t="s">
         <v>33</v>
       </c>
@@ -24129,7 +24130,7 @@
       </c>
       <c r="G11" s="10"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" ht="16">
       <c r="A12" s="14" t="s">
         <v>42</v>
       </c>
@@ -24150,7 +24151,7 @@
       </c>
       <c r="G12" s="10"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" ht="16">
       <c r="A13" s="14" t="s">
         <v>45</v>
       </c>
@@ -24171,7 +24172,7 @@
       </c>
       <c r="G13" s="10"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" ht="16">
       <c r="A14" s="14" t="s">
         <v>54</v>
       </c>
@@ -24192,7 +24193,7 @@
       </c>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" ht="16.5" customHeight="1">
       <c r="A15" s="14" t="s">
         <v>57</v>
       </c>
@@ -24213,7 +24214,7 @@
       </c>
       <c r="G15" s="10"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" ht="16">
       <c r="A16" s="14" t="s">
         <v>68</v>
       </c>
@@ -24234,7 +24235,7 @@
       </c>
       <c r="G16" s="10"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" ht="16">
       <c r="A17" s="14" t="s">
         <v>70</v>
       </c>
@@ -24255,7 +24256,7 @@
       </c>
       <c r="G17" s="10"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" ht="16">
       <c r="A18" s="14" t="s">
         <v>102</v>
       </c>
@@ -24276,7 +24277,7 @@
       </c>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" ht="13.5" customHeight="1">
       <c r="A19" s="14" t="s">
         <v>71</v>
       </c>
@@ -24298,7 +24299,7 @@
       <c r="G19" s="15"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" ht="16">
       <c r="A20" s="14" t="s">
         <v>72</v>
       </c>
@@ -24319,7 +24320,7 @@
       </c>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" ht="16">
       <c r="A21" s="14" t="s">
         <v>76</v>
       </c>
@@ -24340,7 +24341,7 @@
       </c>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" ht="16">
       <c r="A22" s="10" t="s">
         <v>82</v>
       </c>
@@ -24361,7 +24362,7 @@
       </c>
       <c r="G22" s="10"/>
     </row>
-    <row r="23" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" s="20" customFormat="1">
       <c r="A23" s="17" t="s">
         <v>112</v>
       </c>
@@ -24383,7 +24384,7 @@
       <c r="G23" s="18"/>
       <c r="I23" s="5"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" ht="16">
       <c r="A24" s="14" t="s">
         <v>85</v>
       </c>
@@ -24404,7 +24405,7 @@
       </c>
       <c r="G24" s="10"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" ht="16">
       <c r="A25" s="14" t="s">
         <v>86</v>
       </c>
@@ -24425,7 +24426,7 @@
       </c>
       <c r="G25" s="10"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" ht="16">
       <c r="A26" s="14" t="s">
         <v>87</v>
       </c>
@@ -24446,7 +24447,7 @@
       </c>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" ht="16">
       <c r="A27" s="14" t="s">
         <v>88</v>
       </c>
@@ -24467,7 +24468,7 @@
       </c>
       <c r="G27" s="10"/>
     </row>
-    <row r="28" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" ht="8.25" customHeight="1">
       <c r="C28" s="21" t="s">
         <v>113</v>
       </c>
@@ -24484,7 +24485,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" ht="16">
       <c r="B29" s="7" t="s">
         <v>104</v>
       </c>
@@ -24504,7 +24505,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" ht="16">
       <c r="A30" s="14" t="s">
         <v>110</v>
       </c>
@@ -24525,7 +24526,7 @@
       </c>
       <c r="G30" s="10"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" ht="16">
       <c r="A31" s="14" t="s">
         <v>114</v>
       </c>
@@ -24546,7 +24547,7 @@
       </c>
       <c r="G31" s="10"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" ht="16">
       <c r="A32" s="10" t="s">
         <v>110</v>
       </c>
@@ -24567,7 +24568,7 @@
       </c>
       <c r="G32" s="22"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" ht="16">
       <c r="A33" s="10" t="s">
         <v>114</v>
       </c>
@@ -24588,7 +24589,7 @@
       </c>
       <c r="G33" s="22"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" ht="16">
       <c r="A34" s="10" t="s">
         <v>115</v>
       </c>
@@ -24609,18 +24610,18 @@
       </c>
       <c r="G34" s="22"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7">
       <c r="A36" s="289" t="s">
         <v>513</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G27"/>
+  <autoFilter ref="A3:G27" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:G27">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:G27" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>$I$4:$I$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -24636,30 +24637,29 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q225"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.53125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="13.86328125" style="23" customWidth="1"/>
-    <col min="4" max="4" width="14.46484375" style="23" customWidth="1"/>
+    <col min="1" max="1" width="8.5" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5" style="23" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="23" customWidth="1"/>
     <col min="5" max="5" width="13" style="23" customWidth="1"/>
-    <col min="6" max="6" width="10.53125" style="23" customWidth="1"/>
-    <col min="7" max="7" width="11.53125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="11.46484375" style="23" customWidth="1"/>
-    <col min="9" max="9" width="10.53125" style="23" customWidth="1"/>
-    <col min="10" max="11" width="12.53125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="23" customWidth="1"/>
+    <col min="7" max="8" width="11.5" style="23" customWidth="1"/>
+    <col min="9" max="9" width="10.5" style="23" customWidth="1"/>
+    <col min="10" max="11" width="12.5" style="23" customWidth="1"/>
     <col min="12" max="12" width="14" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.86328125" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.53125" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5" style="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" style="23" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.53125" style="23" customWidth="1"/>
-    <col min="17" max="17" width="17.53125" style="23" customWidth="1"/>
-    <col min="18" max="16384" width="9.1328125" style="107"/>
+    <col min="16" max="16" width="11.5" style="23" customWidth="1"/>
+    <col min="17" max="17" width="17.5" style="23" customWidth="1"/>
+    <col min="18" max="16384" width="9.1640625" style="107"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:17" ht="21">
       <c r="A1" s="409" t="s">
         <v>519</v>
       </c>
@@ -24680,7 +24680,7 @@
       <c r="P1" s="409"/>
       <c r="Q1" s="409"/>
     </row>
-    <row r="3" spans="1:17" s="28" customFormat="1" ht="126.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" s="28" customFormat="1" ht="126.75" customHeight="1">
       <c r="A3" s="38" t="s">
         <v>7</v>
       </c>
@@ -24733,7 +24733,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17">
       <c r="A4" s="108" t="s">
         <v>265</v>
       </c>
@@ -24764,7 +24764,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" ht="14.5" customHeight="1">
       <c r="A5" s="108" t="s">
         <v>265</v>
       </c>
@@ -24795,7 +24795,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" ht="30">
       <c r="A6" s="110" t="s">
         <v>22</v>
       </c>
@@ -24826,7 +24826,7 @@
         <v>10.51</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" ht="30">
       <c r="A7" s="110" t="s">
         <v>22</v>
       </c>
@@ -24857,7 +24857,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" ht="15.5" customHeight="1">
       <c r="A8" s="110" t="s">
         <v>22</v>
       </c>
@@ -24888,7 +24888,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17">
       <c r="A9" s="110" t="s">
         <v>22</v>
       </c>
@@ -24917,7 +24917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" ht="30">
       <c r="A10" s="110" t="s">
         <v>22</v>
       </c>
@@ -24946,7 +24946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" ht="30">
       <c r="A11" s="110" t="s">
         <v>22</v>
       </c>
@@ -24975,7 +24975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17">
       <c r="A12" s="110" t="s">
         <v>22</v>
       </c>
@@ -25008,7 +25008,7 @@
         <v>2.2899999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17">
       <c r="A13" s="110" t="s">
         <v>22</v>
       </c>
@@ -25037,7 +25037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17">
       <c r="A14" s="110" t="s">
         <v>22</v>
       </c>
@@ -25070,7 +25070,7 @@
         <v>6.1099999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17">
       <c r="A15" s="110" t="s">
         <v>22</v>
       </c>
@@ -25101,7 +25101,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17">
       <c r="A16" s="110" t="s">
         <v>22</v>
       </c>
@@ -25134,7 +25134,7 @@
         <v>2.2800000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:17">
       <c r="A17" s="110" t="s">
         <v>22</v>
       </c>
@@ -25165,7 +25165,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17">
       <c r="A18" s="110" t="s">
         <v>22</v>
       </c>
@@ -25196,7 +25196,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:17">
       <c r="A19" s="110" t="s">
         <v>22</v>
       </c>
@@ -25227,7 +25227,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:17">
       <c r="A20" s="110" t="s">
         <v>22</v>
       </c>
@@ -25262,7 +25262,7 @@
         <v>57.099999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:17">
       <c r="A21" s="110" t="s">
         <v>22</v>
       </c>
@@ -25291,7 +25291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:17">
       <c r="A22" s="110" t="s">
         <v>22</v>
       </c>
@@ -25322,7 +25322,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:17">
       <c r="A23" s="110" t="s">
         <v>22</v>
       </c>
@@ -25351,7 +25351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:17" ht="31.25" customHeight="1">
       <c r="A24" s="110" t="s">
         <v>22</v>
       </c>
@@ -25384,7 +25384,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:17" ht="31.25" customHeight="1">
       <c r="A25" s="110" t="s">
         <v>22</v>
       </c>
@@ -25413,7 +25413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:17">
       <c r="A26" s="110" t="s">
         <v>22</v>
       </c>
@@ -25446,7 +25446,7 @@
         <v>31.39</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:17">
       <c r="A27" s="110" t="s">
         <v>22</v>
       </c>
@@ -25477,7 +25477,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17">
       <c r="A28" s="110" t="s">
         <v>22</v>
       </c>
@@ -25510,7 +25510,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:17">
       <c r="A29" s="110" t="s">
         <v>22</v>
       </c>
@@ -25541,7 +25541,7 @@
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:17">
       <c r="A30" s="110" t="s">
         <v>22</v>
       </c>
@@ -25572,7 +25572,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:17">
       <c r="A31" s="110" t="s">
         <v>22</v>
       </c>
@@ -25601,7 +25601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:17" ht="30">
       <c r="A32" s="110" t="s">
         <v>22</v>
       </c>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:17" ht="30">
       <c r="A33" s="110" t="s">
         <v>22</v>
       </c>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:17" ht="15.5" customHeight="1">
       <c r="A34" s="110" t="s">
         <v>22</v>
       </c>
@@ -25690,7 +25690,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:17" ht="30">
       <c r="A35" s="110" t="s">
         <v>22</v>
       </c>
@@ -25719,7 +25719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:17">
       <c r="A36" s="110" t="s">
         <v>23</v>
       </c>
@@ -25750,7 +25750,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:17">
       <c r="A37" s="110" t="s">
         <v>24</v>
       </c>
@@ -25781,7 +25781,7 @@
         <v>183.66</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:17">
       <c r="A38" s="110" t="s">
         <v>24</v>
       </c>
@@ -25812,7 +25812,7 @@
         <v>12.57</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:17">
       <c r="A39" s="110" t="s">
         <v>24</v>
       </c>
@@ -25843,7 +25843,7 @@
         <v>58.73</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:17">
       <c r="A40" s="110" t="s">
         <v>24</v>
       </c>
@@ -25872,7 +25872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:17">
       <c r="A41" s="110" t="s">
         <v>24</v>
       </c>
@@ -25903,7 +25903,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:17">
       <c r="A42" s="110" t="s">
         <v>24</v>
       </c>
@@ -25934,7 +25934,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:17">
       <c r="A43" s="110" t="s">
         <v>24</v>
       </c>
@@ -25965,7 +25965,7 @@
         <v>110.82</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:17">
       <c r="A44" s="110" t="s">
         <v>24</v>
       </c>
@@ -25996,7 +25996,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:17">
       <c r="A45" s="110" t="s">
         <v>24</v>
       </c>
@@ -26029,7 +26029,7 @@
         <v>442.05</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:17">
       <c r="A46" s="110" t="s">
         <v>24</v>
       </c>
@@ -26060,7 +26060,7 @@
         <v>9.9400000000000013</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:17">
       <c r="A47" s="110" t="s">
         <v>24</v>
       </c>
@@ -26089,7 +26089,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:17">
       <c r="A48" s="110" t="s">
         <v>24</v>
       </c>
@@ -26118,7 +26118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:17" ht="30">
       <c r="A49" s="110" t="s">
         <v>24</v>
       </c>
@@ -26153,7 +26153,7 @@
         <v>121.6</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:17" ht="30">
       <c r="A50" s="110" t="s">
         <v>24</v>
       </c>
@@ -26184,7 +26184,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="41.65" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:17" ht="45">
       <c r="A51" s="110" t="s">
         <v>27</v>
       </c>
@@ -26217,7 +26217,7 @@
         <v>0.56500000000000006</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="41.65" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:17" ht="45">
       <c r="A52" s="110" t="s">
         <v>27</v>
       </c>
@@ -26246,7 +26246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:17">
       <c r="A53" s="110" t="s">
         <v>31</v>
       </c>
@@ -26281,7 +26281,7 @@
         <v>3701.12</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:17">
       <c r="A54" s="110" t="s">
         <v>31</v>
       </c>
@@ -26316,7 +26316,7 @@
         <v>152.86999999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:17">
       <c r="A55" s="110" t="s">
         <v>31</v>
       </c>
@@ -26355,7 +26355,7 @@
         <v>41.97</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:17">
       <c r="A56" s="110" t="s">
         <v>31</v>
       </c>
@@ -26392,7 +26392,7 @@
         <v>64.349999999999994</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="55.5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:17" ht="60">
       <c r="A57" s="110" t="s">
         <v>33</v>
       </c>
@@ -26423,7 +26423,7 @@
         <v>0.13714942999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="55.5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:17" ht="60">
       <c r="A58" s="110" t="s">
         <v>33</v>
       </c>
@@ -26452,7 +26452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="41.65" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:17" ht="45">
       <c r="A59" s="110" t="s">
         <v>33</v>
       </c>
@@ -26487,7 +26487,7 @@
         <v>110.85396600000001</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="41.65" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:17" ht="45">
       <c r="A60" s="110" t="s">
         <v>33</v>
       </c>
@@ -26516,7 +26516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="41.65" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:17" ht="45">
       <c r="A61" s="110" t="s">
         <v>33</v>
       </c>
@@ -26549,7 +26549,7 @@
         <v>1.5945284200000001</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="41.65" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:17" ht="45">
       <c r="A62" s="110" t="s">
         <v>33</v>
       </c>
@@ -26580,7 +26580,7 @@
         <v>0.15724582999999998</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" ht="30">
       <c r="A63" s="110" t="s">
         <v>33</v>
       </c>
@@ -26613,7 +26613,7 @@
         <v>5.9514991699999999</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:17" ht="30">
       <c r="A64" s="110" t="s">
         <v>33</v>
       </c>
@@ -26642,7 +26642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="55.5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:17" ht="60">
       <c r="A65" s="110" t="s">
         <v>33</v>
       </c>
@@ -26675,7 +26675,7 @@
         <v>0.33244068000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="55.5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:17" ht="60">
       <c r="A66" s="110" t="s">
         <v>33</v>
       </c>
@@ -26704,7 +26704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="69.400000000000006" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:17" ht="75">
       <c r="A67" s="110" t="s">
         <v>33</v>
       </c>
@@ -26737,7 +26737,7 @@
         <v>88.118094020000001</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="69.400000000000006" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:17" ht="75">
       <c r="A68" s="110" t="s">
         <v>33</v>
       </c>
@@ -26768,7 +26768,7 @@
         <v>3.26158E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="41.65" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:17" ht="60">
       <c r="A69" s="110" t="s">
         <v>33</v>
       </c>
@@ -26801,7 +26801,7 @@
         <v>7.4688599999999994E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="41.65" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:17" ht="60">
       <c r="A70" s="110" t="s">
         <v>33</v>
       </c>
@@ -26832,7 +26832,7 @@
         <v>0.15521807999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:17" ht="30">
       <c r="A71" s="110" t="s">
         <v>33</v>
       </c>
@@ -26865,7 +26865,7 @@
         <v>2.50951E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="62.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:17" ht="62.5" customHeight="1">
       <c r="A72" s="110" t="s">
         <v>33</v>
       </c>
@@ -26894,7 +26894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="62.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:17" ht="62.5" customHeight="1">
       <c r="A73" s="110" t="s">
         <v>42</v>
       </c>
@@ -26927,7 +26927,7 @@
         <v>3771.2599999999998</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:17">
       <c r="A74" s="110" t="s">
         <v>42</v>
       </c>
@@ -26960,7 +26960,7 @@
         <v>96.61</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:17">
       <c r="A75" s="110" t="s">
         <v>42</v>
       </c>
@@ -26993,7 +26993,7 @@
         <v>2025.27</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:17">
       <c r="A76" s="110" t="s">
         <v>42</v>
       </c>
@@ -27026,7 +27026,7 @@
         <v>187.53</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:17" ht="30">
       <c r="A77" s="110" t="s">
         <v>45</v>
       </c>
@@ -27057,7 +27057,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:17" ht="30">
       <c r="A78" s="110" t="s">
         <v>45</v>
       </c>
@@ -27088,7 +27088,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:17" ht="30">
       <c r="A79" s="110" t="s">
         <v>45</v>
       </c>
@@ -27119,7 +27119,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:17" ht="15.5" customHeight="1">
       <c r="A80" s="110" t="s">
         <v>45</v>
       </c>
@@ -27150,7 +27150,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:17">
       <c r="A81" s="110" t="s">
         <v>45</v>
       </c>
@@ -27181,7 +27181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:17" ht="15.5" customHeight="1">
       <c r="A82" s="110" t="s">
         <v>45</v>
       </c>
@@ -27212,7 +27212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:17">
       <c r="A83" s="110" t="s">
         <v>49</v>
       </c>
@@ -27241,7 +27241,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:17" ht="15.5" customHeight="1">
       <c r="A84" s="110" t="s">
         <v>49</v>
       </c>
@@ -27270,7 +27270,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:17">
       <c r="A85" s="110" t="s">
         <v>49</v>
       </c>
@@ -27305,7 +27305,7 @@
         <v>119.36</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:17">
       <c r="A86" s="110" t="s">
         <v>49</v>
       </c>
@@ -27334,7 +27334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:17">
       <c r="A87" s="110" t="s">
         <v>49</v>
       </c>
@@ -27365,7 +27365,7 @@
         <v>40.65</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:17">
       <c r="A88" s="110" t="s">
         <v>49</v>
       </c>
@@ -27394,7 +27394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:17">
       <c r="A89" s="110" t="s">
         <v>54</v>
       </c>
@@ -27423,7 +27423,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:17" ht="15.5" customHeight="1">
       <c r="A90" s="110" t="s">
         <v>54</v>
       </c>
@@ -27452,7 +27452,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:17">
       <c r="A91" s="110" t="s">
         <v>54</v>
       </c>
@@ -27483,7 +27483,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:17">
       <c r="A92" s="110" t="s">
         <v>54</v>
       </c>
@@ -27510,7 +27510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:17">
       <c r="A93" s="110" t="s">
         <v>57</v>
       </c>
@@ -27543,7 +27543,7 @@
         <v>39844.92</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:17" ht="15.5" customHeight="1">
       <c r="A94" s="110" t="s">
         <v>57</v>
       </c>
@@ -27574,7 +27574,7 @@
         <v>1239.72</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:17">
       <c r="A95" s="110" t="s">
         <v>57</v>
       </c>
@@ -27603,7 +27603,7 @@
         <v>11484.39</v>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:17" ht="31.25" customHeight="1">
       <c r="A96" s="110" t="s">
         <v>57</v>
       </c>
@@ -27632,7 +27632,7 @@
         <v>4698.2700000000004</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:17" ht="31.25" customHeight="1">
       <c r="A97" s="110" t="s">
         <v>57</v>
       </c>
@@ -27661,7 +27661,7 @@
         <v>1660.84</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:17" ht="15.5" customHeight="1">
       <c r="A98" s="110" t="s">
         <v>57</v>
       </c>
@@ -27690,7 +27690,7 @@
         <v>733.09</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:17">
       <c r="A99" s="110" t="s">
         <v>57</v>
       </c>
@@ -27731,7 +27731,7 @@
         <v>35750.720000000008</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:17" ht="15.5" customHeight="1">
       <c r="A100" s="110" t="s">
         <v>57</v>
       </c>
@@ -27762,7 +27762,7 @@
         <v>502.53</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:17">
       <c r="A101" s="110" t="s">
         <v>57</v>
       </c>
@@ -27803,7 +27803,7 @@
         <v>732.07000000000016</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:17">
       <c r="A102" s="110" t="s">
         <v>57</v>
       </c>
@@ -27836,7 +27836,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:17">
       <c r="A103" s="110" t="s">
         <v>57</v>
       </c>
@@ -27865,7 +27865,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:17" ht="15.5" customHeight="1">
       <c r="A104" s="110" t="s">
         <v>57</v>
       </c>
@@ -27894,7 +27894,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:17">
       <c r="A105" s="110" t="s">
         <v>57</v>
       </c>
@@ -27925,7 +27925,7 @@
         <v>225.21</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:17" ht="15.5" customHeight="1">
       <c r="A106" s="110" t="s">
         <v>57</v>
       </c>
@@ -27954,7 +27954,7 @@
         <v>15.53</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:17">
       <c r="A107" s="110" t="s">
         <v>57</v>
       </c>
@@ -27981,7 +27981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:17" ht="15.5" customHeight="1">
       <c r="A108" s="110" t="s">
         <v>57</v>
       </c>
@@ -28008,7 +28008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:17" ht="30">
       <c r="A109" s="110" t="s">
         <v>57</v>
       </c>
@@ -28039,7 +28039,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:17" ht="15.5" customHeight="1">
       <c r="A110" s="110" t="s">
         <v>57</v>
       </c>
@@ -28066,7 +28066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:17">
       <c r="A111" s="110" t="s">
         <v>57</v>
       </c>
@@ -28093,7 +28093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:17" ht="15.5" customHeight="1">
       <c r="A112" s="110" t="s">
         <v>57</v>
       </c>
@@ -28120,7 +28120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:17">
       <c r="A113" s="110" t="s">
         <v>57</v>
       </c>
@@ -28149,7 +28149,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:17" ht="15.5" customHeight="1">
       <c r="A114" s="110" t="s">
         <v>57</v>
       </c>
@@ -28176,7 +28176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:17">
       <c r="A115" s="110" t="s">
         <v>57</v>
       </c>
@@ -28203,7 +28203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:17" ht="15.5" customHeight="1">
       <c r="A116" s="110" t="s">
         <v>57</v>
       </c>
@@ -28230,7 +28230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:17">
       <c r="A117" s="110" t="s">
         <v>68</v>
       </c>
@@ -28259,7 +28259,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:17" ht="15.5" customHeight="1">
       <c r="A118" s="110" t="s">
         <v>68</v>
       </c>
@@ -28288,7 +28288,7 @@
         <v>466.89</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:17">
       <c r="A119" s="110" t="s">
         <v>68</v>
       </c>
@@ -28317,7 +28317,7 @@
         <v>7.53</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:17" ht="15.5" customHeight="1">
       <c r="A120" s="110" t="s">
         <v>68</v>
       </c>
@@ -28344,7 +28344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:17">
       <c r="A121" s="110" t="s">
         <v>72</v>
       </c>
@@ -28375,7 +28375,7 @@
         <v>237.16</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:17" ht="31.25" customHeight="1">
       <c r="A122" s="110" t="s">
         <v>72</v>
       </c>
@@ -28404,7 +28404,7 @@
         <v>67.05</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:17" ht="31.25" customHeight="1">
       <c r="A123" s="110" t="s">
         <v>72</v>
       </c>
@@ -28435,7 +28435,7 @@
         <v>95.98</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:17">
       <c r="A124" s="110" t="s">
         <v>72</v>
       </c>
@@ -28464,7 +28464,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:17">
       <c r="A125" s="110" t="s">
         <v>73</v>
       </c>
@@ -28501,7 +28501,7 @@
         <v>52.963000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:17">
       <c r="A126" s="110" t="s">
         <v>73</v>
       </c>
@@ -28532,7 +28532,7 @@
         <v>18.249000000000002</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:17">
       <c r="A127" s="110" t="s">
         <v>73</v>
       </c>
@@ -28563,7 +28563,7 @@
         <v>2.4009999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:17" ht="15.5" customHeight="1">
       <c r="A128" s="110" t="s">
         <v>73</v>
       </c>
@@ -28592,7 +28592,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:17" ht="30">
       <c r="A129" s="110" t="s">
         <v>76</v>
       </c>
@@ -28621,7 +28621,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:17" ht="15.5" customHeight="1">
       <c r="A130" s="110" t="s">
         <v>76</v>
       </c>
@@ -28650,7 +28650,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:17" ht="30">
       <c r="A131" s="110" t="s">
         <v>76</v>
       </c>
@@ -28679,7 +28679,7 @@
         <v>166.67</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:17" ht="15.5" customHeight="1">
       <c r="A132" s="110" t="s">
         <v>76</v>
       </c>
@@ -28706,7 +28706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:17" ht="30">
       <c r="A133" s="110" t="s">
         <v>76</v>
       </c>
@@ -28735,7 +28735,7 @@
         <v>119.59</v>
       </c>
     </row>
-    <row r="134" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:17" ht="15.5" customHeight="1">
       <c r="A134" s="110" t="s">
         <v>76</v>
       </c>
@@ -28762,7 +28762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:17" ht="30">
       <c r="A135" s="110" t="s">
         <v>76</v>
       </c>
@@ -28793,7 +28793,7 @@
         <v>16.04</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:17" ht="15.5" customHeight="1">
       <c r="A136" s="110" t="s">
         <v>76</v>
       </c>
@@ -28822,7 +28822,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:17" ht="30">
       <c r="A137" s="110" t="s">
         <v>76</v>
       </c>
@@ -28853,7 +28853,7 @@
         <v>11.64</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:17" ht="15.5" customHeight="1">
       <c r="A138" s="110" t="s">
         <v>76</v>
       </c>
@@ -28882,7 +28882,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:17">
       <c r="A139" s="110" t="s">
         <v>76</v>
       </c>
@@ -28911,7 +28911,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:17">
       <c r="A140" s="110" t="s">
         <v>76</v>
       </c>
@@ -28938,7 +28938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:17">
       <c r="A141" s="110" t="s">
         <v>76</v>
       </c>
@@ -28967,7 +28967,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:17" ht="15.5" customHeight="1">
       <c r="A142" s="110" t="s">
         <v>76</v>
       </c>
@@ -28996,7 +28996,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:17">
       <c r="A143" s="110" t="s">
         <v>76</v>
       </c>
@@ -29023,7 +29023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:17" ht="15.5" customHeight="1">
       <c r="A144" s="110" t="s">
         <v>76</v>
       </c>
@@ -29052,7 +29052,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:17">
       <c r="A145" s="110" t="s">
         <v>76</v>
       </c>
@@ -29081,7 +29081,7 @@
         <v>8.9999999999999998E-4</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:17">
       <c r="A146" s="110" t="s">
         <v>76</v>
       </c>
@@ -29108,7 +29108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:17">
       <c r="A147" s="113" t="s">
         <v>82</v>
       </c>
@@ -29145,7 +29145,7 @@
         <v>3100.4</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:17">
       <c r="A148" s="113" t="s">
         <v>82</v>
       </c>
@@ -29180,7 +29180,7 @@
         <v>571.76</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:17">
       <c r="A149" s="113" t="s">
         <v>82</v>
       </c>
@@ -29217,7 +29217,7 @@
         <v>3431.29</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:17">
       <c r="A150" s="113" t="s">
         <v>82</v>
       </c>
@@ -29254,7 +29254,7 @@
         <v>770.2</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:17">
       <c r="A151" s="113" t="s">
         <v>82</v>
       </c>
@@ -29281,7 +29281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:17">
       <c r="A152" s="113" t="s">
         <v>82</v>
       </c>
@@ -29308,7 +29308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:17">
       <c r="A153" s="110" t="s">
         <v>85</v>
       </c>
@@ -29339,7 +29339,7 @@
         <v>16762.649999999998</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:17">
       <c r="A154" s="110" t="s">
         <v>87</v>
       </c>
@@ -29366,7 +29366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:17">
       <c r="A155" s="110" t="s">
         <v>87</v>
       </c>
@@ -29393,7 +29393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:17">
       <c r="A156" s="110" t="s">
         <v>87</v>
       </c>
@@ -29422,7 +29422,7 @@
         <v>1368.92</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:17">
       <c r="A157" s="110" t="s">
         <v>87</v>
       </c>
@@ -29451,7 +29451,7 @@
         <v>450.82</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:17">
       <c r="A158" s="110" t="s">
         <v>87</v>
       </c>
@@ -29480,7 +29480,7 @@
         <v>722.81</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:17">
       <c r="A159" s="110" t="s">
         <v>87</v>
       </c>
@@ -29509,7 +29509,7 @@
         <v>167.36</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:17">
       <c r="A160" s="110" t="s">
         <v>87</v>
       </c>
@@ -29538,7 +29538,7 @@
         <v>129.62</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:17">
       <c r="A161" s="110" t="s">
         <v>87</v>
       </c>
@@ -29567,7 +29567,7 @@
         <v>78.03</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:17">
       <c r="A162" s="110" t="s">
         <v>87</v>
       </c>
@@ -29598,7 +29598,7 @@
         <v>3.8400000000000003</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:17">
       <c r="A163" s="110" t="s">
         <v>87</v>
       </c>
@@ -29627,7 +29627,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:17" ht="15.5" customHeight="1">
       <c r="A164" s="110" t="s">
         <v>87</v>
       </c>
@@ -29660,7 +29660,7 @@
         <v>117.69999999999999</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:17">
       <c r="A165" s="110" t="s">
         <v>87</v>
       </c>
@@ -29689,7 +29689,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="166" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:17" ht="15.5" customHeight="1">
       <c r="A166" s="110" t="s">
         <v>87</v>
       </c>
@@ -29720,7 +29720,7 @@
         <v>6.6400000000000006</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:17">
       <c r="A167" s="110" t="s">
         <v>87</v>
       </c>
@@ -29749,7 +29749,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:17">
       <c r="A168" s="110" t="s">
         <v>87</v>
       </c>
@@ -29780,7 +29780,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:17">
       <c r="A169" s="110" t="s">
         <v>87</v>
       </c>
@@ -29807,7 +29807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:17">
       <c r="A170" s="110" t="s">
         <v>87</v>
       </c>
@@ -29844,7 +29844,7 @@
         <v>6.6199999999999992</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:17">
       <c r="A171" s="110" t="s">
         <v>87</v>
       </c>
@@ -29873,7 +29873,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:17">
       <c r="A172" s="110" t="s">
         <v>87</v>
       </c>
@@ -29900,7 +29900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:17">
       <c r="A173" s="110" t="s">
         <v>87</v>
       </c>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:17">
       <c r="A174" s="110" t="s">
         <v>87</v>
       </c>
@@ -29958,7 +29958,7 @@
         <v>12.56</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:17">
       <c r="A175" s="110" t="s">
         <v>87</v>
       </c>
@@ -29985,7 +29985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:17">
       <c r="A176" s="110" t="s">
         <v>87</v>
       </c>
@@ -30016,7 +30016,7 @@
         <v>218.4</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:17">
       <c r="A177" s="110" t="s">
         <v>87</v>
       </c>
@@ -30047,7 +30047,7 @@
         <v>13.969999999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:17" ht="30">
       <c r="A178" s="110" t="s">
         <v>87</v>
       </c>
@@ -30076,7 +30076,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="179" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:17" ht="30">
       <c r="A179" s="110" t="s">
         <v>87</v>
       </c>
@@ -30105,7 +30105,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:17">
       <c r="A180" s="110" t="s">
         <v>87</v>
       </c>
@@ -30136,7 +30136,7 @@
         <v>47.41</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:17">
       <c r="A181" s="110" t="s">
         <v>87</v>
       </c>
@@ -30163,7 +30163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:17">
       <c r="A182" s="110" t="s">
         <v>87</v>
       </c>
@@ -30192,7 +30192,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:17">
       <c r="A183" s="110" t="s">
         <v>87</v>
       </c>
@@ -30219,7 +30219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:17">
       <c r="A184" s="110" t="s">
         <v>87</v>
       </c>
@@ -30248,7 +30248,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:17">
       <c r="A185" s="110" t="s">
         <v>87</v>
       </c>
@@ -30275,7 +30275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:17">
       <c r="A186" s="110" t="s">
         <v>87</v>
       </c>
@@ -30302,7 +30302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:17">
       <c r="A187" s="110" t="s">
         <v>87</v>
       </c>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:17">
       <c r="A188" s="110" t="s">
         <v>87</v>
       </c>
@@ -30356,7 +30356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:17">
       <c r="A189" s="110" t="s">
         <v>87</v>
       </c>
@@ -30383,7 +30383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:17">
       <c r="A190" s="110" t="s">
         <v>87</v>
       </c>
@@ -30410,7 +30410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:17">
       <c r="A191" s="110" t="s">
         <v>87</v>
       </c>
@@ -30437,7 +30437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:17">
       <c r="A192" s="110" t="s">
         <v>88</v>
       </c>
@@ -30472,7 +30472,7 @@
         <v>63.04</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:17">
       <c r="A193" s="110" t="s">
         <v>88</v>
       </c>
@@ -30501,7 +30501,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="194" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:17" ht="31.25" customHeight="1">
       <c r="A194" s="110" t="s">
         <v>88</v>
       </c>
@@ -30534,7 +30534,7 @@
         <v>30.52</v>
       </c>
     </row>
-    <row r="195" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:17" ht="31.25" customHeight="1">
       <c r="A195" s="110" t="s">
         <v>88</v>
       </c>
@@ -30565,7 +30565,7 @@
         <v>23.35</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:17">
       <c r="A196" s="113" t="s">
         <v>88</v>
       </c>
@@ -30600,7 +30600,7 @@
         <v>3568.1722</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:17">
       <c r="A197" s="113" t="s">
         <v>88</v>
       </c>
@@ -30629,7 +30629,7 @@
         <v>19.072800000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:17" ht="30">
       <c r="A198" s="113" t="s">
         <v>88</v>
       </c>
@@ -30664,7 +30664,7 @@
         <v>1176.4100000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:17" ht="30">
       <c r="A199" s="113" t="s">
         <v>88</v>
       </c>
@@ -30693,7 +30693,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="200" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:17" ht="30">
       <c r="A200" s="113" t="s">
         <v>88</v>
       </c>
@@ -30728,7 +30728,7 @@
         <v>27.470000000000002</v>
       </c>
     </row>
-    <row r="201" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:17" ht="30">
       <c r="A201" s="113" t="s">
         <v>88</v>
       </c>
@@ -30759,7 +30759,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:17">
       <c r="A202" s="113" t="s">
         <v>88</v>
       </c>
@@ -30790,7 +30790,7 @@
         <v>22.240000000000002</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:17">
       <c r="A203" s="113" t="s">
         <v>88</v>
       </c>
@@ -30819,7 +30819,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:17">
       <c r="A204" s="113" t="s">
         <v>88</v>
       </c>
@@ -30854,7 +30854,7 @@
         <v>256.15899999999999</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:17">
       <c r="A205" s="113" t="s">
         <v>88</v>
       </c>
@@ -30885,7 +30885,7 @@
         <v>120.41800000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:17">
       <c r="A206" s="113" t="s">
         <v>88</v>
       </c>
@@ -30922,7 +30922,7 @@
         <v>120.90600000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:17">
       <c r="A207" s="113" t="s">
         <v>88</v>
       </c>
@@ -30953,7 +30953,7 @@
         <v>6.1909999999999998</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:17">
       <c r="A208" s="113" t="s">
         <v>88</v>
       </c>
@@ -30982,7 +30982,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:17">
       <c r="A209" s="113" t="s">
         <v>88</v>
       </c>
@@ -31011,7 +31011,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="210" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:17" ht="15.5" customHeight="1">
       <c r="A210" s="113" t="s">
         <v>88</v>
       </c>
@@ -31040,7 +31040,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:17" ht="30">
       <c r="A211" s="113" t="s">
         <v>88</v>
       </c>
@@ -31067,7 +31067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:17" ht="15.5" customHeight="1">
       <c r="A212" s="113" t="s">
         <v>88</v>
       </c>
@@ -31096,7 +31096,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:17" ht="30">
       <c r="A213" s="113" t="s">
         <v>88</v>
       </c>
@@ -31125,7 +31125,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:17" ht="30">
       <c r="A214" s="113" t="s">
         <v>88</v>
       </c>
@@ -31154,7 +31154,7 @@
         <v>0.36299999999999999</v>
       </c>
     </row>
-    <row r="215" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:17" ht="30">
       <c r="A215" s="113" t="s">
         <v>88</v>
       </c>
@@ -31183,7 +31183,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="216" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:17" ht="30">
       <c r="A216" s="113" t="s">
         <v>88</v>
       </c>
@@ -31218,7 +31218,7 @@
         <v>0.8650000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:17" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:17" ht="30">
       <c r="A217" s="113" t="s">
         <v>88</v>
       </c>
@@ -31245,7 +31245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:17">
       <c r="A218" s="113" t="s">
         <v>88</v>
       </c>
@@ -31278,7 +31278,7 @@
         <v>24.786000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:17">
       <c r="A219" s="113" t="s">
         <v>88</v>
       </c>
@@ -31307,7 +31307,7 @@
         <v>7.2930000000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:17" ht="16">
       <c r="A220" s="27"/>
       <c r="B220" s="26"/>
       <c r="C220" s="26"/>
@@ -31326,7 +31326,7 @@
       <c r="P220" s="305"/>
       <c r="Q220" s="305"/>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:17">
       <c r="A221" s="306"/>
       <c r="B221" s="306"/>
       <c r="C221" s="306"/>
@@ -31345,7 +31345,7 @@
       <c r="P221" s="307"/>
       <c r="Q221" s="307"/>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:17">
       <c r="D222" s="24"/>
       <c r="E222" s="24"/>
       <c r="F222" s="24"/>
@@ -31361,7 +31361,7 @@
       <c r="P222" s="24"/>
       <c r="Q222" s="24"/>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:17">
       <c r="A223" s="33" t="s">
         <v>154</v>
       </c>
@@ -31408,14 +31408,14 @@
         <v>144444.53570132004</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:17">
       <c r="M224" s="25"/>
     </row>
-    <row r="225" spans="13:13" x14ac:dyDescent="0.45">
+    <row r="225" spans="13:13">
       <c r="M225" s="25"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q220"/>
+  <autoFilter ref="A3:Q220" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
@@ -31430,39 +31430,39 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AG34"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.86328125" style="78" customWidth="1"/>
-    <col min="2" max="2" width="17.1328125" style="78" customWidth="1"/>
-    <col min="3" max="4" width="14.1328125" style="78" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.46484375" style="78" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" style="78" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" style="78" customWidth="1"/>
+    <col min="3" max="4" width="14.1640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" style="78" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.6640625" style="78" customWidth="1"/>
     <col min="7" max="7" width="7.33203125" style="78" customWidth="1"/>
-    <col min="8" max="9" width="12.46484375" style="78" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.5" style="78" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.33203125" style="78" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="3.1328125" style="78" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="3.1640625" style="78" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.6640625" style="78" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.46484375" style="78" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="8.46484375" style="78" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="6.53125" style="78" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.46484375" style="78" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="3.1328125" style="78" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.46484375" style="78" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5" style="78" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="8.5" style="78" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="6.5" style="78" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.5" style="78" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="3.1640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5" style="78" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="12" style="78" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.1328125" style="78" customWidth="1"/>
+    <col min="25" max="25" width="9.1640625" style="78" customWidth="1"/>
     <col min="26" max="27" width="7" style="78" customWidth="1"/>
     <col min="28" max="28" width="16.33203125" style="78" customWidth="1"/>
     <col min="29" max="29" width="13.6640625" style="78" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.53125" style="78" customWidth="1"/>
-    <col min="31" max="31" width="3.86328125" style="78" customWidth="1"/>
-    <col min="32" max="32" width="15.1328125" style="78" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.1328125" style="78" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.1328125" style="78"/>
+    <col min="30" max="30" width="2.5" style="78" customWidth="1"/>
+    <col min="31" max="31" width="3.83203125" style="78" customWidth="1"/>
+    <col min="32" max="32" width="15.1640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.1640625" style="78"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:33">
       <c r="B1" s="415" t="s">
         <v>405</v>
       </c>
@@ -31498,7 +31498,7 @@
       <c r="AF1" s="415"/>
       <c r="AG1" s="415"/>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:33">
       <c r="B2" s="416" t="s">
         <v>152</v>
       </c>
@@ -31534,7 +31534,7 @@
       <c r="AF2" s="416"/>
       <c r="AG2" s="416"/>
     </row>
-    <row r="3" spans="1:33" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:33" ht="16" thickBot="1">
       <c r="B3" s="417" t="s">
         <v>116</v>
       </c>
@@ -31570,7 +31570,7 @@
       <c r="AF3" s="417"/>
       <c r="AG3" s="417"/>
     </row>
-    <row r="4" spans="1:33" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:33" ht="16" thickBot="1">
       <c r="A4" s="79"/>
       <c r="B4" s="79"/>
       <c r="C4" s="419" t="s">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="AG4" s="423"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:33">
       <c r="A5" s="80"/>
       <c r="B5" s="123"/>
       <c r="C5" s="410" t="s">
@@ -31656,7 +31656,7 @@
       <c r="AF5" s="424"/>
       <c r="AG5" s="425"/>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:33">
       <c r="A6" s="80"/>
       <c r="B6" s="123"/>
       <c r="C6" s="412"/>
@@ -31691,7 +31691,7 @@
       <c r="AF6" s="424"/>
       <c r="AG6" s="425"/>
     </row>
-    <row r="7" spans="1:33" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:33" ht="57.75" customHeight="1">
       <c r="A7" s="326" t="s">
         <v>7</v>
       </c>
@@ -31792,7 +31792,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:33" ht="32">
       <c r="A8" s="329" t="s">
         <v>31</v>
       </c>
@@ -31845,7 +31845,7 @@
       <c r="AF8" s="312"/>
       <c r="AG8" s="312"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:33" ht="16">
       <c r="A9" s="329" t="s">
         <v>42</v>
       </c>
@@ -31884,7 +31884,7 @@
       <c r="AF9" s="318"/>
       <c r="AG9" s="318"/>
     </row>
-    <row r="10" spans="1:33" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:33" ht="32">
       <c r="A10" s="329" t="s">
         <v>57</v>
       </c>
@@ -31923,7 +31923,7 @@
       <c r="AF10" s="312"/>
       <c r="AG10" s="312"/>
     </row>
-    <row r="11" spans="1:33" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:33" ht="32">
       <c r="A11" s="329" t="s">
         <v>57</v>
       </c>
@@ -31966,7 +31966,7 @@
         <v>12267.7</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:33" ht="32">
       <c r="A12" s="329" t="s">
         <v>57</v>
       </c>
@@ -32009,7 +32009,7 @@
         <v>22.02</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:33" ht="32">
       <c r="A13" s="329" t="s">
         <v>57</v>
       </c>
@@ -32062,7 +32062,7 @@
       <c r="AF13" s="312"/>
       <c r="AG13" s="312"/>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:33" ht="16">
       <c r="A14" s="329" t="s">
         <v>57</v>
       </c>
@@ -32105,7 +32105,7 @@
         <v>316.88</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:33" ht="32">
       <c r="A15" s="329" t="s">
         <v>57</v>
       </c>
@@ -32144,7 +32144,7 @@
       <c r="AF15" s="312"/>
       <c r="AG15" s="312"/>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:33" ht="16">
       <c r="A16" s="329" t="s">
         <v>57</v>
       </c>
@@ -32187,7 +32187,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:33" ht="32">
       <c r="A17" s="329" t="s">
         <v>57</v>
       </c>
@@ -32240,7 +32240,7 @@
       <c r="AF17" s="312"/>
       <c r="AG17" s="312"/>
     </row>
-    <row r="18" spans="1:33" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:33" ht="32">
       <c r="A18" s="329" t="s">
         <v>57</v>
       </c>
@@ -32293,7 +32293,7 @@
       <c r="AF18" s="312"/>
       <c r="AG18" s="312"/>
     </row>
-    <row r="19" spans="1:33" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:33" ht="32">
       <c r="A19" s="329" t="s">
         <v>57</v>
       </c>
@@ -32356,7 +32356,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:33" ht="32">
       <c r="A20" s="329" t="s">
         <v>57</v>
       </c>
@@ -32419,7 +32419,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:33" ht="48">
       <c r="A21" s="329" t="s">
         <v>57</v>
       </c>
@@ -32462,7 +32462,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:33" ht="48">
       <c r="A22" s="329" t="s">
         <v>57</v>
       </c>
@@ -32513,7 +32513,7 @@
       <c r="AF22" s="312"/>
       <c r="AG22" s="312"/>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:33" ht="16">
       <c r="A23" s="329" t="s">
         <v>82</v>
       </c>
@@ -32566,7 +32566,7 @@
       <c r="AF23" s="312"/>
       <c r="AG23" s="312"/>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:33" ht="16">
       <c r="A24" s="329" t="s">
         <v>82</v>
       </c>
@@ -32619,7 +32619,7 @@
       <c r="AF24" s="312"/>
       <c r="AG24" s="312"/>
     </row>
-    <row r="25" spans="1:33" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:33" ht="32">
       <c r="A25" s="329" t="s">
         <v>87</v>
       </c>
@@ -32658,7 +32658,7 @@
       <c r="AF25" s="318"/>
       <c r="AG25" s="318"/>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:33" ht="16">
       <c r="A26" s="329" t="s">
         <v>88</v>
       </c>
@@ -32711,7 +32711,7 @@
       <c r="AF26" s="312"/>
       <c r="AG26" s="312"/>
     </row>
-    <row r="27" spans="1:33" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:33" ht="48">
       <c r="A27" s="329" t="s">
         <v>88</v>
       </c>
@@ -32750,7 +32750,7 @@
       <c r="AF27" s="322"/>
       <c r="AG27" s="322"/>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:33" ht="16">
       <c r="A28" s="329" t="s">
         <v>88</v>
       </c>
@@ -32793,7 +32793,7 @@
         <v>0.98299999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:33" ht="16">
       <c r="A29" s="332"/>
       <c r="B29" s="332" t="s">
         <v>118</v>
@@ -32858,12 +32858,12 @@
         <v>12627.093000000003</v>
       </c>
     </row>
-    <row r="34" spans="33:33" x14ac:dyDescent="0.45">
+    <row r="34" spans="33:33">
       <c r="AG34" s="195"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:AG28">
-    <sortState ref="A8:AG27">
+  <autoFilter ref="A7:AG28" xr:uid="{00000000-0009-0000-0000-000005000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:AG27">
       <sortCondition ref="A7:A26"/>
     </sortState>
   </autoFilter>
@@ -32892,28 +32892,28 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A2:P36"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="29" customWidth="1"/>
     <col min="2" max="3" width="10.33203125" style="29" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1328125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1328125" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.86328125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.83203125" style="29" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="29" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.46484375" style="32" customWidth="1"/>
-    <col min="15" max="16" width="14.1328125" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.1328125" style="29"/>
+    <col min="12" max="12" width="13.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5" style="32" customWidth="1"/>
+    <col min="15" max="16" width="14.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.1640625" style="29"/>
     <col min="18" max="18" width="11.33203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29"/>
+    <col min="19" max="16384" width="9.1640625" style="29"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" ht="16">
       <c r="A2" s="428" t="s">
         <v>408</v>
       </c>
@@ -32933,7 +32933,7 @@
       <c r="O2" s="428"/>
       <c r="P2" s="428"/>
     </row>
-    <row r="3" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" ht="16">
       <c r="A3" s="429" t="s">
         <v>116</v>
       </c>
@@ -32953,7 +32953,7 @@
       <c r="O3" s="429"/>
       <c r="P3" s="429"/>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" ht="16">
       <c r="A4" s="30"/>
       <c r="B4" s="430" t="s">
         <v>142</v>
@@ -32975,7 +32975,7 @@
       </c>
       <c r="P4" s="431"/>
     </row>
-    <row r="5" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" ht="16">
       <c r="A5" s="30"/>
       <c r="B5" s="430" t="s">
         <v>144</v>
@@ -33005,7 +33005,7 @@
       <c r="O5" s="431"/>
       <c r="P5" s="431"/>
     </row>
-    <row r="6" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" ht="29.25" customHeight="1">
       <c r="A6" s="30"/>
       <c r="B6" s="430"/>
       <c r="C6" s="431"/>
@@ -33023,7 +33023,7 @@
       <c r="O6" s="431"/>
       <c r="P6" s="431"/>
     </row>
-    <row r="7" spans="1:16" ht="74.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" ht="74.25" customHeight="1">
       <c r="A7" s="74" t="s">
         <v>7</v>
       </c>
@@ -33071,7 +33071,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16">
       <c r="A8" s="337" t="s">
         <v>265</v>
       </c>
@@ -33095,7 +33095,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16">
       <c r="A9" s="337" t="s">
         <v>22</v>
       </c>
@@ -33119,7 +33119,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16">
       <c r="A10" s="337" t="s">
         <v>510</v>
       </c>
@@ -33147,7 +33147,7 @@
         <v>5.4170000000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16">
       <c r="A11" s="337" t="s">
         <v>511</v>
       </c>
@@ -33171,7 +33171,7 @@
         <v>718.57999999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16">
       <c r="A12" s="337" t="s">
         <v>103</v>
       </c>
@@ -33195,7 +33195,7 @@
         <v>29.160844999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16">
       <c r="A13" s="337" t="s">
         <v>27</v>
       </c>
@@ -33219,7 +33219,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16">
       <c r="A14" s="337" t="s">
         <v>29</v>
       </c>
@@ -33263,7 +33263,7 @@
         <v>6.2870000000000008</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16">
       <c r="A15" s="337" t="s">
         <v>31</v>
       </c>
@@ -33291,7 +33291,7 @@
       <c r="O15" s="339"/>
       <c r="P15" s="339"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16">
       <c r="A16" s="337" t="s">
         <v>33</v>
       </c>
@@ -33331,7 +33331,7 @@
         <v>1.8917925999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:16">
       <c r="A17" s="337" t="s">
         <v>42</v>
       </c>
@@ -33355,7 +33355,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:16">
       <c r="A18" s="337" t="s">
         <v>45</v>
       </c>
@@ -33391,7 +33391,7 @@
         <v>4.6120000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16">
       <c r="A19" s="337" t="s">
         <v>49</v>
       </c>
@@ -33423,7 +33423,7 @@
         <v>11.172000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16">
       <c r="A20" s="337" t="s">
         <v>54</v>
       </c>
@@ -33455,7 +33455,7 @@
         <v>32.33</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:16">
       <c r="A21" s="337" t="s">
         <v>57</v>
       </c>
@@ -33489,7 +33489,7 @@
         <v>12738.520000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16">
       <c r="A22" s="337" t="s">
         <v>68</v>
       </c>
@@ -33525,7 +33525,7 @@
         <v>850.72</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16">
       <c r="A23" s="337" t="s">
         <v>70</v>
       </c>
@@ -33553,7 +33553,7 @@
         <v>4.5540000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16">
       <c r="A24" s="337" t="s">
         <v>102</v>
       </c>
@@ -33577,7 +33577,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16">
       <c r="A25" s="337" t="s">
         <v>71</v>
       </c>
@@ -33601,7 +33601,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16">
       <c r="A26" s="337" t="s">
         <v>72</v>
       </c>
@@ -33625,7 +33625,7 @@
         <v>243.24</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:16">
       <c r="A27" s="337" t="s">
         <v>73</v>
       </c>
@@ -33649,7 +33649,7 @@
         <v>67.87</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16">
       <c r="A28" s="337" t="s">
         <v>76</v>
       </c>
@@ -33673,7 +33673,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:16">
       <c r="A29" s="337" t="s">
         <v>112</v>
       </c>
@@ -33713,7 +33713,7 @@
         <v>16.72</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:16">
       <c r="A30" s="337" t="s">
         <v>82</v>
       </c>
@@ -33749,7 +33749,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:16">
       <c r="A31" s="337" t="s">
         <v>85</v>
       </c>
@@ -33793,7 +33793,7 @@
         <v>1.5622293699999998</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:16">
       <c r="A32" s="337" t="s">
         <v>86</v>
       </c>
@@ -33817,7 +33817,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:16">
       <c r="A33" s="337" t="s">
         <v>87</v>
       </c>
@@ -33861,7 +33861,7 @@
         <v>1041.58</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:16">
       <c r="A34" s="337" t="s">
         <v>88</v>
       </c>
@@ -33897,7 +33897,7 @@
         <v>16.827000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:16">
       <c r="B36" s="196"/>
       <c r="C36" s="196"/>
       <c r="D36" s="196"/>
@@ -33939,26 +33939,26 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Q77"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.53125" style="40" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.46484375" style="40" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="40" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="16" style="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.46484375" style="40" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="40" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="16" style="40" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.46484375" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="40" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="16" style="40" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" style="40" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" style="40" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="16" style="40" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.46484375" style="40" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5" style="40" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="16" style="40" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.1328125" style="40"/>
+    <col min="18" max="16384" width="9.1640625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" ht="16">
       <c r="B1" s="433"/>
       <c r="C1" s="433"/>
       <c r="D1" s="433"/>
@@ -33976,7 +33976,7 @@
       <c r="P1" s="433"/>
       <c r="Q1" s="433"/>
     </row>
-    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" ht="16">
       <c r="B2" s="434" t="s">
         <v>520</v>
       </c>
@@ -33996,7 +33996,7 @@
       <c r="P2" s="434"/>
       <c r="Q2" s="434"/>
     </row>
-    <row r="3" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" ht="16">
       <c r="B3" s="435"/>
       <c r="C3" s="435"/>
       <c r="D3" s="435"/>
@@ -34014,7 +34014,7 @@
       <c r="P3" s="435"/>
       <c r="Q3" s="435"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="358"/>
       <c r="B4" s="359"/>
       <c r="C4" s="436"/>
@@ -34033,7 +34033,7 @@
       <c r="P4" s="437"/>
       <c r="Q4" s="437"/>
     </row>
-    <row r="5" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" ht="16">
       <c r="A5" s="360"/>
       <c r="B5" s="361"/>
       <c r="C5" s="439" t="s">
@@ -34062,7 +34062,7 @@
       <c r="P5" s="439"/>
       <c r="Q5" s="440"/>
     </row>
-    <row r="6" spans="1:17" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:17" ht="17.25" customHeight="1" thickBot="1">
       <c r="A6" s="362"/>
       <c r="B6" s="363"/>
       <c r="C6" s="442"/>
@@ -34081,7 +34081,7 @@
       <c r="P6" s="442"/>
       <c r="Q6" s="443"/>
     </row>
-    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" ht="51" customHeight="1">
       <c r="A7" s="357" t="s">
         <v>7</v>
       </c>
@@ -34134,7 +34134,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" s="349" customFormat="1">
       <c r="A8" s="348" t="s">
         <v>23</v>
       </c>
@@ -34161,7 +34161,7 @@
       <c r="P8" s="313"/>
       <c r="Q8" s="313"/>
     </row>
-    <row r="9" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" s="349" customFormat="1">
       <c r="A9" s="348" t="s">
         <v>23</v>
       </c>
@@ -34188,7 +34188,7 @@
       <c r="P9" s="313"/>
       <c r="Q9" s="313"/>
     </row>
-    <row r="10" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" s="349" customFormat="1">
       <c r="A10" s="348" t="s">
         <v>23</v>
       </c>
@@ -34215,7 +34215,7 @@
       <c r="P10" s="313"/>
       <c r="Q10" s="313"/>
     </row>
-    <row r="11" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" s="349" customFormat="1">
       <c r="A11" s="348" t="s">
         <v>23</v>
       </c>
@@ -34242,7 +34242,7 @@
       <c r="P11" s="313"/>
       <c r="Q11" s="313"/>
     </row>
-    <row r="12" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" s="349" customFormat="1">
       <c r="A12" s="348" t="s">
         <v>23</v>
       </c>
@@ -34273,7 +34273,7 @@
       <c r="P12" s="313"/>
       <c r="Q12" s="313"/>
     </row>
-    <row r="13" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17" s="349" customFormat="1">
       <c r="A13" s="348" t="s">
         <v>23</v>
       </c>
@@ -34300,7 +34300,7 @@
       <c r="P13" s="313"/>
       <c r="Q13" s="313"/>
     </row>
-    <row r="14" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17" s="349" customFormat="1">
       <c r="A14" s="348" t="s">
         <v>23</v>
       </c>
@@ -34331,7 +34331,7 @@
       <c r="P14" s="313"/>
       <c r="Q14" s="313"/>
     </row>
-    <row r="15" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17" s="349" customFormat="1">
       <c r="A15" s="348" t="s">
         <v>23</v>
       </c>
@@ -34362,7 +34362,7 @@
       <c r="P15" s="313"/>
       <c r="Q15" s="313"/>
     </row>
-    <row r="16" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" s="349" customFormat="1">
       <c r="A16" s="348" t="s">
         <v>23</v>
       </c>
@@ -34393,7 +34393,7 @@
       <c r="P16" s="313"/>
       <c r="Q16" s="313"/>
     </row>
-    <row r="17" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:17" s="349" customFormat="1">
       <c r="A17" s="348" t="s">
         <v>23</v>
       </c>
@@ -34424,7 +34424,7 @@
       <c r="P17" s="313"/>
       <c r="Q17" s="313"/>
     </row>
-    <row r="18" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17" s="349" customFormat="1">
       <c r="A18" s="348" t="s">
         <v>23</v>
       </c>
@@ -34451,7 +34451,7 @@
       <c r="P18" s="313"/>
       <c r="Q18" s="313"/>
     </row>
-    <row r="19" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:17" s="349" customFormat="1">
       <c r="A19" s="348" t="s">
         <v>23</v>
       </c>
@@ -34482,7 +34482,7 @@
       <c r="P19" s="313"/>
       <c r="Q19" s="313"/>
     </row>
-    <row r="20" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:17" s="349" customFormat="1">
       <c r="A20" s="348" t="s">
         <v>23</v>
       </c>
@@ -34509,7 +34509,7 @@
       <c r="P20" s="313"/>
       <c r="Q20" s="313"/>
     </row>
-    <row r="21" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:17" s="349" customFormat="1">
       <c r="A21" s="348" t="s">
         <v>29</v>
       </c>
@@ -34542,7 +34542,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:17" s="349" customFormat="1">
       <c r="A22" s="348" t="s">
         <v>29</v>
       </c>
@@ -34577,7 +34577,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:17" s="349" customFormat="1">
       <c r="A23" s="348" t="s">
         <v>29</v>
       </c>
@@ -34612,7 +34612,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:17" s="349" customFormat="1">
       <c r="A24" s="348" t="s">
         <v>29</v>
       </c>
@@ -34647,7 +34647,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:17" s="349" customFormat="1">
       <c r="A25" s="348" t="s">
         <v>29</v>
       </c>
@@ -34692,7 +34692,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:17" s="349" customFormat="1">
       <c r="A26" s="348" t="s">
         <v>31</v>
       </c>
@@ -34721,7 +34721,7 @@
       <c r="P26" s="313"/>
       <c r="Q26" s="313"/>
     </row>
-    <row r="27" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:17" s="349" customFormat="1">
       <c r="A27" s="348" t="s">
         <v>33</v>
       </c>
@@ -34762,7 +34762,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17" s="349" customFormat="1">
       <c r="A28" s="348" t="s">
         <v>45</v>
       </c>
@@ -34791,7 +34791,7 @@
       <c r="P28" s="313"/>
       <c r="Q28" s="313"/>
     </row>
-    <row r="29" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:17" s="349" customFormat="1">
       <c r="A29" s="348" t="s">
         <v>45</v>
       </c>
@@ -34820,7 +34820,7 @@
       <c r="P29" s="313"/>
       <c r="Q29" s="313"/>
     </row>
-    <row r="30" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:17" s="349" customFormat="1">
       <c r="A30" s="348" t="s">
         <v>45</v>
       </c>
@@ -34849,7 +34849,7 @@
       <c r="P30" s="313"/>
       <c r="Q30" s="313"/>
     </row>
-    <row r="31" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:17" s="349" customFormat="1">
       <c r="A31" s="348" t="s">
         <v>45</v>
       </c>
@@ -34878,7 +34878,7 @@
       <c r="P31" s="313"/>
       <c r="Q31" s="313"/>
     </row>
-    <row r="32" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:17" s="349" customFormat="1">
       <c r="A32" s="348" t="s">
         <v>45</v>
       </c>
@@ -34907,7 +34907,7 @@
       <c r="P32" s="313"/>
       <c r="Q32" s="313"/>
     </row>
-    <row r="33" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:17" s="349" customFormat="1">
       <c r="A33" s="348" t="s">
         <v>45</v>
       </c>
@@ -34934,7 +34934,7 @@
       <c r="P33" s="313"/>
       <c r="Q33" s="313"/>
     </row>
-    <row r="34" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:17" s="349" customFormat="1">
       <c r="A34" s="348" t="s">
         <v>49</v>
       </c>
@@ -34963,7 +34963,7 @@
       <c r="P34" s="313"/>
       <c r="Q34" s="313"/>
     </row>
-    <row r="35" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:17" s="349" customFormat="1">
       <c r="A35" s="348" t="s">
         <v>49</v>
       </c>
@@ -34992,7 +34992,7 @@
       <c r="P35" s="313"/>
       <c r="Q35" s="313"/>
     </row>
-    <row r="36" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:17" s="349" customFormat="1">
       <c r="A36" s="348" t="s">
         <v>49</v>
       </c>
@@ -35015,7 +35015,7 @@
       <c r="P36" s="313"/>
       <c r="Q36" s="313"/>
     </row>
-    <row r="37" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:17" s="349" customFormat="1">
       <c r="A37" s="348" t="s">
         <v>49</v>
       </c>
@@ -35044,7 +35044,7 @@
       <c r="P37" s="313"/>
       <c r="Q37" s="313"/>
     </row>
-    <row r="38" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:17" s="349" customFormat="1">
       <c r="A38" s="348" t="s">
         <v>49</v>
       </c>
@@ -35073,7 +35073,7 @@
       <c r="P38" s="313"/>
       <c r="Q38" s="313"/>
     </row>
-    <row r="39" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:17" s="349" customFormat="1">
       <c r="A39" s="348" t="s">
         <v>49</v>
       </c>
@@ -35102,7 +35102,7 @@
       <c r="P39" s="313"/>
       <c r="Q39" s="313"/>
     </row>
-    <row r="40" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:17" s="349" customFormat="1">
       <c r="A40" s="348" t="s">
         <v>54</v>
       </c>
@@ -35131,7 +35131,7 @@
       <c r="P40" s="313"/>
       <c r="Q40" s="313"/>
     </row>
-    <row r="41" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:17" s="349" customFormat="1">
       <c r="A41" s="348" t="s">
         <v>57</v>
       </c>
@@ -35160,7 +35160,7 @@
       <c r="P41" s="313"/>
       <c r="Q41" s="313"/>
     </row>
-    <row r="42" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:17" s="349" customFormat="1">
       <c r="A42" s="348" t="s">
         <v>57</v>
       </c>
@@ -35189,7 +35189,7 @@
       <c r="P42" s="313"/>
       <c r="Q42" s="313"/>
     </row>
-    <row r="43" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:17" s="349" customFormat="1">
       <c r="A43" s="348" t="s">
         <v>57</v>
       </c>
@@ -35218,7 +35218,7 @@
       <c r="P43" s="313"/>
       <c r="Q43" s="313"/>
     </row>
-    <row r="44" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:17" s="349" customFormat="1">
       <c r="A44" s="348" t="s">
         <v>68</v>
       </c>
@@ -35247,7 +35247,7 @@
       <c r="P44" s="313"/>
       <c r="Q44" s="313"/>
     </row>
-    <row r="45" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:17" s="349" customFormat="1">
       <c r="A45" s="348" t="s">
         <v>68</v>
       </c>
@@ -35276,7 +35276,7 @@
         <v>0.77190000000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:17" s="349" customFormat="1">
       <c r="A46" s="348" t="s">
         <v>68</v>
       </c>
@@ -35305,7 +35305,7 @@
       <c r="P46" s="313"/>
       <c r="Q46" s="313"/>
     </row>
-    <row r="47" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:17" s="349" customFormat="1">
       <c r="A47" s="352" t="s">
         <v>82</v>
       </c>
@@ -35334,7 +35334,7 @@
       <c r="P47" s="313"/>
       <c r="Q47" s="313"/>
     </row>
-    <row r="48" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:17" s="349" customFormat="1">
       <c r="A48" s="352" t="s">
         <v>82</v>
       </c>
@@ -35363,7 +35363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:17" s="349" customFormat="1">
       <c r="A49" s="352" t="s">
         <v>82</v>
       </c>
@@ -35392,7 +35392,7 @@
       <c r="P49" s="313"/>
       <c r="Q49" s="313"/>
     </row>
-    <row r="50" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:17" s="349" customFormat="1">
       <c r="A50" s="352" t="s">
         <v>82</v>
       </c>
@@ -35421,7 +35421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:17" s="349" customFormat="1">
       <c r="A51" s="348" t="s">
         <v>112</v>
       </c>
@@ -35450,7 +35450,7 @@
       <c r="P51" s="355"/>
       <c r="Q51" s="355"/>
     </row>
-    <row r="52" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:17" s="349" customFormat="1">
       <c r="A52" s="348" t="s">
         <v>112</v>
       </c>
@@ -35479,7 +35479,7 @@
       <c r="P52" s="355"/>
       <c r="Q52" s="355"/>
     </row>
-    <row r="53" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:17" s="349" customFormat="1">
       <c r="A53" s="348" t="s">
         <v>112</v>
       </c>
@@ -35508,7 +35508,7 @@
       <c r="P53" s="355"/>
       <c r="Q53" s="355"/>
     </row>
-    <row r="54" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:17" s="349" customFormat="1">
       <c r="A54" s="348" t="s">
         <v>112</v>
       </c>
@@ -35537,7 +35537,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:17" s="349" customFormat="1">
       <c r="A55" s="348" t="s">
         <v>112</v>
       </c>
@@ -35566,7 +35566,7 @@
       <c r="P55" s="355"/>
       <c r="Q55" s="355"/>
     </row>
-    <row r="56" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:17" s="349" customFormat="1">
       <c r="A56" s="348" t="s">
         <v>85</v>
       </c>
@@ -35595,7 +35595,7 @@
       <c r="P56" s="313"/>
       <c r="Q56" s="313"/>
     </row>
-    <row r="57" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:17" s="349" customFormat="1">
       <c r="A57" s="348" t="s">
         <v>85</v>
       </c>
@@ -35630,7 +35630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:17" s="349" customFormat="1">
       <c r="A58" s="348" t="s">
         <v>85</v>
       </c>
@@ -35665,7 +35665,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:17" s="349" customFormat="1">
       <c r="A59" s="348" t="s">
         <v>85</v>
       </c>
@@ -35706,7 +35706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:17" s="349" customFormat="1">
       <c r="A60" s="348" t="s">
         <v>85</v>
       </c>
@@ -35741,7 +35741,7 @@
       <c r="P60" s="313"/>
       <c r="Q60" s="313"/>
     </row>
-    <row r="61" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:17" s="349" customFormat="1">
       <c r="A61" s="348" t="s">
         <v>85</v>
       </c>
@@ -35776,7 +35776,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:17" s="349" customFormat="1">
       <c r="A62" s="348" t="s">
         <v>85</v>
       </c>
@@ -35811,7 +35811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" s="349" customFormat="1">
       <c r="A63" s="348" t="s">
         <v>85</v>
       </c>
@@ -35840,7 +35840,7 @@
       <c r="P63" s="313"/>
       <c r="Q63" s="313"/>
     </row>
-    <row r="64" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:17" s="349" customFormat="1">
       <c r="A64" s="348" t="s">
         <v>85</v>
       </c>
@@ -35875,7 +35875,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:17" s="349" customFormat="1">
       <c r="A65" s="348" t="s">
         <v>85</v>
       </c>
@@ -35910,7 +35910,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:17" s="349" customFormat="1">
       <c r="A66" s="348" t="s">
         <v>85</v>
       </c>
@@ -35945,7 +35945,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:17" s="349" customFormat="1">
       <c r="A67" s="348" t="s">
         <v>85</v>
       </c>
@@ -35980,7 +35980,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:17" s="349" customFormat="1">
       <c r="A68" s="348" t="s">
         <v>85</v>
       </c>
@@ -36015,7 +36015,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:17" s="349" customFormat="1">
       <c r="A69" s="348" t="s">
         <v>85</v>
       </c>
@@ -36050,7 +36050,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:17" s="349" customFormat="1">
       <c r="A70" s="348" t="s">
         <v>87</v>
       </c>
@@ -36079,7 +36079,7 @@
       <c r="P70" s="313"/>
       <c r="Q70" s="313"/>
     </row>
-    <row r="71" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:17" s="349" customFormat="1">
       <c r="A71" s="348" t="s">
         <v>87</v>
       </c>
@@ -36108,7 +36108,7 @@
       <c r="P71" s="313"/>
       <c r="Q71" s="313"/>
     </row>
-    <row r="72" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:17" s="349" customFormat="1">
       <c r="A72" s="348" t="s">
         <v>87</v>
       </c>
@@ -36137,7 +36137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:17" s="349" customFormat="1">
       <c r="A73" s="348" t="s">
         <v>87</v>
       </c>
@@ -36166,7 +36166,7 @@
       <c r="P73" s="313"/>
       <c r="Q73" s="313"/>
     </row>
-    <row r="74" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:17" s="349" customFormat="1">
       <c r="A74" s="352" t="s">
         <v>88</v>
       </c>
@@ -36195,7 +36195,7 @@
       <c r="P74" s="313"/>
       <c r="Q74" s="313"/>
     </row>
-    <row r="75" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:17" s="349" customFormat="1">
       <c r="A75" s="352" t="s">
         <v>88</v>
       </c>
@@ -36224,7 +36224,7 @@
       <c r="P75" s="313"/>
       <c r="Q75" s="313"/>
     </row>
-    <row r="76" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:17" s="349" customFormat="1">
       <c r="A76" s="352" t="s">
         <v>88</v>
       </c>
@@ -36253,7 +36253,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="349" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:17" s="349" customFormat="1">
       <c r="A77" s="352" t="s">
         <v>88</v>
       </c>
@@ -36283,7 +36283,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:Q77"/>
+  <autoFilter ref="A7:Q77" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <mergeCells count="9">
     <mergeCell ref="B1:Q1"/>
     <mergeCell ref="B2:Q2"/>
@@ -36306,31 +36306,31 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.75" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="14" style="378" customWidth="1"/>
-    <col min="2" max="2" width="11.1328125" style="378" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="378" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" style="378" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="378"/>
-    <col min="5" max="5" width="11.1328125" style="378" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" style="378" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.6640625" style="378" customWidth="1"/>
     <col min="7" max="7" width="8.6640625" style="378"/>
-    <col min="8" max="8" width="11.1328125" style="378" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" style="378" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.6640625" style="378" customWidth="1"/>
     <col min="10" max="10" width="8.6640625" style="378"/>
-    <col min="11" max="11" width="11.1328125" style="378" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.86328125" style="378" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" style="378" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" style="378" customWidth="1"/>
     <col min="13" max="13" width="8.6640625" style="378"/>
-    <col min="14" max="14" width="12.86328125" style="378" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" style="378" customWidth="1"/>
     <col min="15" max="15" width="13.33203125" style="378" customWidth="1"/>
     <col min="16" max="16" width="8.6640625" style="378"/>
     <col min="17" max="17" width="12.33203125" style="378" customWidth="1"/>
     <col min="18" max="18" width="14.33203125" style="378" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.6640625" style="378"/>
-    <col min="20" max="20" width="12.86328125" style="378" customWidth="1"/>
-    <col min="21" max="21" width="12.46484375" style="378" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" style="378" customWidth="1"/>
+    <col min="21" max="21" width="12.5" style="378" customWidth="1"/>
     <col min="22" max="22" width="8.6640625" style="378"/>
     <col min="23" max="23" width="13.33203125" style="378" customWidth="1"/>
     <col min="24" max="24" width="12.6640625" style="378" customWidth="1"/>
@@ -36338,7 +36338,7 @@
     <col min="26" max="16384" width="8.6640625" style="378"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:25" ht="28.5" customHeight="1">
       <c r="A1" s="444" t="s">
         <v>521</v>
       </c>
@@ -36367,7 +36367,7 @@
       <c r="X1" s="444"/>
       <c r="Y1" s="444"/>
     </row>
-    <row r="2" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:25" ht="45.75" customHeight="1">
       <c r="A2" s="364"/>
       <c r="B2" s="445" t="s">
         <v>244</v>
@@ -36410,7 +36410,7 @@
       <c r="X2" s="445"/>
       <c r="Y2" s="445"/>
     </row>
-    <row r="3" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:25" ht="31.5" customHeight="1">
       <c r="A3" s="365" t="s">
         <v>7</v>
       </c>
@@ -36487,7 +36487,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:25" ht="15" customHeight="1">
       <c r="A4" s="370" t="s">
         <v>265</v>
       </c>
@@ -36550,7 +36550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:25" ht="15" customHeight="1">
       <c r="A5" s="370" t="s">
         <v>22</v>
       </c>
@@ -36627,7 +36627,7 @@
         <v>0.91348600508905864</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:25" ht="15" customHeight="1">
       <c r="A6" s="370" t="s">
         <v>23</v>
       </c>
@@ -36696,7 +36696,7 @@
         <v>1.0992288961038958</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:25" ht="15" customHeight="1">
       <c r="A7" s="370" t="s">
         <v>24</v>
       </c>
@@ -36773,7 +36773,7 @@
         <v>1.6213081834796148</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:25" ht="15" customHeight="1">
       <c r="A8" s="370" t="s">
         <v>103</v>
       </c>
@@ -36850,7 +36850,7 @@
         <v>0.92763684744181651</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:25" ht="15" customHeight="1">
       <c r="A9" s="370" t="s">
         <v>27</v>
       </c>
@@ -36915,7 +36915,7 @@
         <v>3.8265306122448974E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:25" ht="15" customHeight="1">
       <c r="A10" s="370" t="s">
         <v>29</v>
       </c>
@@ -36992,7 +36992,7 @@
         <v>0.83731583508728491</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:25" ht="15" customHeight="1">
       <c r="A11" s="370" t="s">
         <v>31</v>
       </c>
@@ -37063,7 +37063,7 @@
         <v>0.7878098189712921</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:25" ht="15" customHeight="1">
       <c r="A12" s="370" t="s">
         <v>33</v>
       </c>
@@ -37140,7 +37140,7 @@
         <v>0.11153864557302985</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:25" ht="15" customHeight="1">
       <c r="A13" s="370" t="s">
         <v>42</v>
       </c>
@@ -37209,7 +37209,7 @@
         <v>0.1714261646028136</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:25" ht="15" customHeight="1">
       <c r="A14" s="370" t="s">
         <v>45</v>
       </c>
@@ -37280,7 +37280,7 @@
         <v>0.80585831062670299</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:25" ht="15" customHeight="1">
       <c r="A15" s="370" t="s">
         <v>49</v>
       </c>
@@ -37349,7 +37349,7 @@
         <v>0.25045407868021152</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:25" ht="15" customHeight="1">
       <c r="A16" s="370" t="s">
         <v>54</v>
       </c>
@@ -37426,7 +37426,7 @@
         <v>0.81209578744974653</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:25" ht="15" customHeight="1">
       <c r="A17" s="370" t="s">
         <v>57</v>
       </c>
@@ -37499,7 +37499,7 @@
         <v>0.84877103853704272</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:25" ht="15" customHeight="1">
       <c r="A18" s="370" t="s">
         <v>68</v>
       </c>
@@ -37568,7 +37568,7 @@
         <v>0.32926389513637699</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:25" ht="15" customHeight="1">
       <c r="A19" s="370" t="s">
         <v>517</v>
       </c>
@@ -37603,7 +37603,7 @@
         <v>0.87138127326964743</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:25" ht="15" customHeight="1">
       <c r="A20" s="370" t="s">
         <v>70</v>
       </c>
@@ -37672,7 +37672,7 @@
         <v>0.65868781542898347</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:25" ht="15" customHeight="1">
       <c r="A21" s="370" t="s">
         <v>102</v>
       </c>
@@ -37737,7 +37737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:25" ht="15" customHeight="1">
       <c r="A22" s="370" t="s">
         <v>71</v>
       </c>
@@ -37804,7 +37804,7 @@
         <v>0.9729669347631813</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:25" ht="15" customHeight="1">
       <c r="A23" s="370" t="s">
         <v>72</v>
       </c>
@@ -37873,7 +37873,7 @@
         <v>0.75965021861336668</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:25" ht="15" customHeight="1">
       <c r="A24" s="370" t="s">
         <v>73</v>
       </c>
@@ -37942,7 +37942,7 @@
         <v>0.95997171145686</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:25" ht="15" customHeight="1">
       <c r="A25" s="370" t="s">
         <v>76</v>
       </c>
@@ -38011,7 +38011,7 @@
         <v>0.67387687188019962</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:25" ht="15" customHeight="1">
       <c r="A26" s="370" t="s">
         <v>82</v>
       </c>
@@ -38086,7 +38086,7 @@
         <v>0.13308789394434825</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:25" ht="15" customHeight="1">
       <c r="A27" s="370" t="s">
         <v>112</v>
       </c>
@@ -38159,7 +38159,7 @@
         <v>0.82309469499001131</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:25" ht="15" customHeight="1">
       <c r="A28" s="370" t="s">
         <v>85</v>
       </c>
@@ -38236,7 +38236,7 @@
         <v>0.85190676137168786</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:25" ht="15" customHeight="1">
       <c r="A29" s="370" t="s">
         <v>86</v>
       </c>
@@ -38307,7 +38307,7 @@
         <v>0.33719095213045763</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:25" ht="15" customHeight="1">
       <c r="A30" s="370" t="s">
         <v>87</v>
       </c>
@@ -38378,7 +38378,7 @@
         <v>0.88958708955798449</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:25" ht="15" customHeight="1">
       <c r="A31" s="370" t="s">
         <v>88</v>
       </c>
@@ -38453,7 +38453,7 @@
         <v>0.81533833840419423</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:25" ht="15" customHeight="1">
       <c r="A32" s="370" t="s">
         <v>118</v>
       </c>
@@ -38530,9 +38530,9 @@
         <v>0.44372411636717274</v>
       </c>
     </row>
-    <row r="35" ht="21" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="35" ht="21" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A3:Y32"/>
+  <autoFilter ref="A3:Y32" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <mergeCells count="9">
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="E2:G2"/>
@@ -38552,4 +38552,10 @@
 Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{3de9faa6-9fe1-49b3-9a08-227a296b54a6}" enabled="1" method="Privileged" siteId="{66d73691-ea97-48b1-95d5-e94f0a46b878}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>